--- a/Deliverables/BOM/eSpark_BOM.xlsx
+++ b/Deliverables/BOM/eSpark_BOM.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-switchbox\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ezlo-switchbox\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51668318-96EA-426C-9780-581526948A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="10 Boards" sheetId="1" r:id="rId1"/>
     <sheet name="1000 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="255">
   <si>
     <t>Component list</t>
   </si>
@@ -733,12 +732,66 @@
   </si>
   <si>
     <t>C12018</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>WJ2EDGK-5.08-3P</t>
+  </si>
+  <si>
+    <t>C71371</t>
+  </si>
+  <si>
+    <t>KF2EDGK-5.08-4P-AA</t>
+  </si>
+  <si>
+    <t>3 1 5.08mm Green Plug P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>320V 15A 4 2.5 1 12~24 5.08mm Green Plug P=5.08mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>Cixi Kefa Elec</t>
+  </si>
+  <si>
+    <t>C440882</t>
+  </si>
+  <si>
+    <t>BWIPX1-SMA-1.13L100</t>
+  </si>
+  <si>
+    <t>TX2400-JKD-20</t>
+  </si>
+  <si>
+    <t>13x200mm Antennas ROHS</t>
+  </si>
+  <si>
+    <t>100mm IPEX to SMA 1Gen - Radio Frequency Cable ROHS</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>ZIISOR</t>
+  </si>
+  <si>
+    <t>C454911</t>
+  </si>
+  <si>
+    <t>C784403</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [switch-box]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -945,7 +998,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1203,12 +1256,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1348,12 +1427,6 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1399,9 +1472,6 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1412,9 +1482,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1463,6 +1530,112 @@
     <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1499,9 +1672,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>1781175</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1529,8 +1702,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29927550" y="620017"/>
-          <a:ext cx="1714500" cy="1104008"/>
+          <a:off x="21116925" y="620017"/>
+          <a:ext cx="1771650" cy="1142108"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1858,9 +2031,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1894,15 +2067,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="82"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1912,8 +2085,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="55" t="s">
-        <v>186</v>
+      <c r="F2" s="53" t="s">
+        <v>253</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1937,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="54" t="s">
         <v>187</v>
       </c>
       <c r="G3" s="13"/>
@@ -1952,7 +2125,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="83"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1962,7 +2135,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="55" t="s">
         <v>187</v>
       </c>
       <c r="G4" s="14"/>
@@ -1977,7 +2150,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="84"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1987,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -2002,7 +2175,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="84"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2023,7 +2196,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="84"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2044,7 +2217,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="84"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2065,23 +2238,23 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="84"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="57" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="30" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="30" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="30" t="s">
@@ -2093,31 +2266,31 @@
       <c r="I9" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="K9" s="59" t="s">
+      <c r="K9" s="31" t="s">
         <v>176</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="M9" s="60" t="s">
+      <c r="M9" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="O9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="Q9" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="R9" s="31" t="s">
+      <c r="R9" s="30" t="s">
         <v>178</v>
       </c>
       <c r="S9" s="30" t="s">
@@ -2126,26 +2299,26 @@
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="37">
+      <c r="B10" s="94">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="45" t="s">
         <v>52</v>
       </c>
       <c r="F10" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="46" t="s">
+      <c r="G10" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="46" t="s">
         <v>124</v>
       </c>
       <c r="I10" s="45" t="s">
@@ -2154,110 +2327,110 @@
       <c r="J10" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K10" s="45" t="s">
+      <c r="K10" s="46" t="s">
         <v>161</v>
       </c>
       <c r="L10" s="52">
         <v>2</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="46">
         <f>L10*10</f>
         <v>20</v>
       </c>
       <c r="N10" s="45">
         <v>40</v>
       </c>
-      <c r="O10" s="63" t="s">
+      <c r="O10" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P10" s="50">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="Q10" s="50">
+      <c r="Q10" s="114">
         <f>P10*N10</f>
         <v>0.95600000000000007</v>
       </c>
-      <c r="R10" s="46"/>
-      <c r="S10" s="53"/>
+      <c r="R10" s="45"/>
+      <c r="S10" s="87"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="37">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="94">
+        <f t="shared" ref="B11:B46" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="48" t="s">
+      <c r="H11" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="J11" s="48" t="s">
+      <c r="J11" s="91" t="s">
         <v>227</v>
       </c>
-      <c r="K11" s="48" t="s">
+      <c r="K11" s="90" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="48">
+      <c r="L11" s="91">
         <v>3</v>
       </c>
-      <c r="M11" s="48">
-        <f t="shared" ref="M11:M42" si="1">L11*10</f>
+      <c r="M11" s="90">
+        <f t="shared" ref="M11:M46" si="1">L11*10</f>
         <v>30</v>
       </c>
-      <c r="N11" s="48">
+      <c r="N11" s="91">
         <v>100</v>
       </c>
-      <c r="O11" s="65" t="s">
+      <c r="O11" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P11" s="51">
+      <c r="P11" s="92">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="Q11" s="51">
-        <f t="shared" ref="Q11:Q42" si="2">P11*N11</f>
+      <c r="Q11" s="115">
+        <f t="shared" ref="Q11:Q46" si="2">P11*N11</f>
         <v>0.3</v>
       </c>
-      <c r="R11" s="49"/>
-      <c r="S11" s="54"/>
+      <c r="R11" s="91"/>
+      <c r="S11" s="93"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="37">
+      <c r="B12" s="94">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="46" t="s">
+      <c r="E12" s="45" t="s">
         <v>54</v>
       </c>
       <c r="F12" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="46" t="s">
+      <c r="G12" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="46" t="s">
         <v>126</v>
       </c>
       <c r="I12" s="45" t="s">
@@ -2266,110 +2439,110 @@
       <c r="J12" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="K12" s="45" t="s">
+      <c r="K12" s="46" t="s">
         <v>163</v>
       </c>
       <c r="L12" s="45">
         <v>1</v>
       </c>
-      <c r="M12" s="45">
+      <c r="M12" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N12" s="45">
         <v>100</v>
       </c>
-      <c r="O12" s="63" t="s">
+      <c r="O12" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P12" s="50">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="114">
         <f t="shared" si="2"/>
         <v>0.45999999999999996</v>
       </c>
-      <c r="R12" s="46"/>
+      <c r="R12" s="45"/>
       <c r="S12" s="50"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="37">
+      <c r="B13" s="94">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="49" t="s">
+      <c r="E13" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="109" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="48" t="s">
+      <c r="H13" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="91" t="s">
         <v>194</v>
       </c>
-      <c r="J13" s="48" t="s">
+      <c r="J13" s="91" t="s">
         <v>195</v>
       </c>
-      <c r="K13" s="48" t="s">
+      <c r="K13" s="90" t="s">
         <v>164</v>
       </c>
-      <c r="L13" s="48">
+      <c r="L13" s="91">
         <v>1</v>
       </c>
-      <c r="M13" s="48">
+      <c r="M13" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N13" s="48">
+      <c r="N13" s="91">
         <v>20</v>
       </c>
-      <c r="O13" s="65" t="s">
+      <c r="O13" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P13" s="51">
+      <c r="P13" s="92">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="Q13" s="51">
+      <c r="Q13" s="115">
         <f t="shared" si="2"/>
         <v>0.46800000000000003</v>
       </c>
-      <c r="R13" s="49"/>
-      <c r="S13" s="51"/>
+      <c r="R13" s="91"/>
+      <c r="S13" s="92"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="37">
+      <c r="B14" s="94">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="66" t="s">
+      <c r="D14" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="45" t="s">
         <v>56</v>
       </c>
       <c r="F14" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="46" t="s">
         <v>126</v>
       </c>
       <c r="I14" s="45" t="s">
@@ -2378,113 +2551,113 @@
       <c r="J14" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="K14" s="45" t="s">
+      <c r="K14" s="46" t="s">
         <v>165</v>
       </c>
       <c r="L14" s="45">
         <v>1</v>
       </c>
-      <c r="M14" s="45">
+      <c r="M14" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N14" s="45">
         <v>50</v>
       </c>
-      <c r="O14" s="63" t="s">
+      <c r="O14" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P14" s="50">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="Q14" s="50">
+      <c r="Q14" s="114">
         <f t="shared" si="2"/>
         <v>0.77999999999999992</v>
       </c>
-      <c r="R14" s="46"/>
+      <c r="R14" s="45"/>
       <c r="S14" s="50"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="37">
+      <c r="B15" s="94">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="H15" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J15" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="K15" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L15" s="48">
+      <c r="G15" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="I15" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="K15" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L15" s="91">
         <v>2</v>
       </c>
-      <c r="M15" s="48">
+      <c r="M15" s="90">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N15" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="O15" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="P15" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q15" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="R15" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="S15" s="48" t="s">
+      <c r="N15" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="O15" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q15" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="R15" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="S15" s="91" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="37">
+      <c r="B16" s="94">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="66" t="s">
+      <c r="D16" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="45" t="s">
         <v>58</v>
       </c>
       <c r="F16" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="46" t="s">
+      <c r="G16" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="46" t="s">
         <v>126</v>
       </c>
       <c r="I16" s="45" t="s">
@@ -2493,110 +2666,110 @@
       <c r="J16" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="K16" s="45" t="s">
+      <c r="K16" s="46" t="s">
         <v>163</v>
       </c>
       <c r="L16" s="45">
         <v>1</v>
       </c>
-      <c r="M16" s="45">
+      <c r="M16" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N16" s="45">
         <v>100</v>
       </c>
-      <c r="O16" s="63" t="s">
+      <c r="O16" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P16" s="50">
         <v>2E-3</v>
       </c>
-      <c r="Q16" s="50">
+      <c r="Q16" s="114">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="R16" s="46"/>
+      <c r="R16" s="45"/>
       <c r="S16" s="50"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="37">
+      <c r="B17" s="94">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="67" t="s">
+      <c r="D17" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="49" t="s">
+      <c r="E17" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="48" t="s">
+      <c r="F17" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="49" t="s">
+      <c r="G17" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="J17" s="48" t="s">
+      <c r="I17" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="K17" s="48" t="s">
+      <c r="K17" s="90" t="s">
         <v>166</v>
       </c>
-      <c r="L17" s="48">
+      <c r="L17" s="91">
         <v>1</v>
       </c>
-      <c r="M17" s="48">
+      <c r="M17" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N17" s="48">
+      <c r="N17" s="91">
         <v>50</v>
       </c>
-      <c r="O17" s="65" t="s">
+      <c r="O17" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P17" s="51">
+      <c r="P17" s="92">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="Q17" s="51">
+      <c r="Q17" s="115">
         <f t="shared" si="2"/>
         <v>0.69499999999999995</v>
       </c>
-      <c r="R17" s="49"/>
-      <c r="S17" s="51"/>
+      <c r="R17" s="91"/>
+      <c r="S17" s="92"/>
     </row>
     <row r="18" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="37">
+      <c r="B18" s="94">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="66" t="s">
+      <c r="D18" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="46" t="s">
+      <c r="E18" s="45" t="s">
         <v>203</v>
       </c>
       <c r="F18" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="G18" s="46" t="s">
+      <c r="G18" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="46" t="s">
         <v>205</v>
       </c>
       <c r="I18" s="45" t="s">
@@ -2605,110 +2778,110 @@
       <c r="J18" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="K18" s="45" t="s">
+      <c r="K18" s="46" t="s">
         <v>207</v>
       </c>
       <c r="L18" s="45">
         <v>2</v>
       </c>
-      <c r="M18" s="45">
+      <c r="M18" s="46">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N18" s="45">
         <v>40</v>
       </c>
-      <c r="O18" s="63" t="s">
+      <c r="O18" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P18" s="50">
         <v>2.75E-2</v>
       </c>
-      <c r="Q18" s="50">
+      <c r="Q18" s="114">
         <f>P18*N18</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="R18" s="46"/>
+      <c r="R18" s="45"/>
       <c r="S18" s="50"/>
     </row>
     <row r="19" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="37">
+      <c r="B19" s="94">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="88" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="49" t="s">
+      <c r="G19" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="48" t="s">
+      <c r="H19" s="90" t="s">
         <v>127</v>
       </c>
-      <c r="I19" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J19" s="48" t="s">
+      <c r="I19" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J19" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="K19" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L19" s="48">
+      <c r="K19" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L19" s="91">
         <v>1</v>
       </c>
-      <c r="M19" s="48">
+      <c r="M19" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N19" s="48">
+      <c r="N19" s="91">
         <v>15</v>
       </c>
-      <c r="O19" s="65" t="s">
+      <c r="O19" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P19" s="51">
+      <c r="P19" s="92">
         <v>6.54E-2</v>
       </c>
-      <c r="Q19" s="51">
+      <c r="Q19" s="115">
         <f t="shared" si="2"/>
         <v>0.98099999999999998</v>
       </c>
-      <c r="R19" s="49"/>
-      <c r="S19" s="51"/>
+      <c r="R19" s="91"/>
+      <c r="S19" s="92"/>
     </row>
     <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="37">
+      <c r="B20" s="94">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="66" t="s">
+      <c r="D20" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="E20" s="45" t="s">
         <v>61</v>
       </c>
       <c r="F20" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="46" t="s">
         <v>128</v>
       </c>
       <c r="I20" s="45" t="s">
@@ -2717,110 +2890,110 @@
       <c r="J20" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="K20" s="45" t="s">
+      <c r="K20" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L20" s="45">
         <v>1</v>
       </c>
-      <c r="M20" s="45">
+      <c r="M20" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N20" s="45">
         <v>15</v>
       </c>
-      <c r="O20" s="63" t="s">
+      <c r="O20" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P20" s="50">
         <v>7.1599999999999997E-2</v>
       </c>
-      <c r="Q20" s="50">
+      <c r="Q20" s="114">
         <f t="shared" si="2"/>
         <v>1.0739999999999998</v>
       </c>
-      <c r="R20" s="46"/>
+      <c r="R20" s="45"/>
       <c r="S20" s="50"/>
     </row>
     <row r="21" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="37">
+      <c r="B21" s="94">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="88" t="s">
         <v>189</v>
       </c>
-      <c r="D21" s="67" t="s">
+      <c r="D21" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="49" t="s">
+      <c r="E21" s="91" t="s">
         <v>208</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="49" t="s">
+      <c r="G21" s="91" t="s">
         <v>209</v>
       </c>
-      <c r="H21" s="48" t="s">
+      <c r="H21" s="90" t="s">
         <v>210</v>
       </c>
-      <c r="I21" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J21" s="48" t="s">
+      <c r="I21" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J21" s="91" t="s">
         <v>209</v>
       </c>
-      <c r="K21" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L21" s="48">
+      <c r="K21" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L21" s="91">
         <v>1</v>
       </c>
-      <c r="M21" s="48">
+      <c r="M21" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N21" s="48">
+      <c r="N21" s="91">
         <v>12</v>
       </c>
-      <c r="O21" s="65" t="s">
+      <c r="O21" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P21" s="51">
+      <c r="P21" s="92">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="Q21" s="51">
+      <c r="Q21" s="115">
         <f t="shared" si="2"/>
         <v>0.86399999999999988</v>
       </c>
-      <c r="R21" s="49"/>
-      <c r="S21" s="51"/>
+      <c r="R21" s="91"/>
+      <c r="S21" s="92"/>
     </row>
     <row r="22" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="37">
+      <c r="B22" s="94">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D22" s="66" t="s">
+      <c r="D22" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="46" t="s">
+      <c r="E22" s="45" t="s">
         <v>62</v>
       </c>
       <c r="F22" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="G22" s="46" t="s">
+      <c r="G22" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="46" t="s">
         <v>129</v>
       </c>
       <c r="I22" s="45" t="s">
@@ -2829,110 +3002,110 @@
       <c r="J22" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="45" t="s">
+      <c r="K22" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L22" s="45">
         <v>1</v>
       </c>
-      <c r="M22" s="45">
+      <c r="M22" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N22" s="45">
         <v>15</v>
       </c>
-      <c r="O22" s="63" t="s">
+      <c r="O22" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P22" s="50">
         <v>0.2276</v>
       </c>
-      <c r="Q22" s="50">
+      <c r="Q22" s="114">
         <f t="shared" si="2"/>
         <v>3.4140000000000001</v>
       </c>
-      <c r="R22" s="46"/>
+      <c r="R22" s="45"/>
       <c r="S22" s="50"/>
     </row>
     <row r="23" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="37">
+      <c r="B23" s="94">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="67" t="s">
+      <c r="D23" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="49" t="s">
+      <c r="E23" s="91" t="s">
         <v>211</v>
       </c>
-      <c r="F23" s="48" t="s">
+      <c r="F23" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="49" t="s">
+      <c r="G23" s="91" t="s">
         <v>212</v>
       </c>
-      <c r="H23" s="48" t="s">
+      <c r="H23" s="90" t="s">
         <v>213</v>
       </c>
-      <c r="I23" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J23" s="48" t="s">
+      <c r="I23" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J23" s="91" t="s">
         <v>214</v>
       </c>
-      <c r="K23" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L23" s="48">
+      <c r="K23" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L23" s="91">
         <v>1</v>
       </c>
-      <c r="M23" s="48">
+      <c r="M23" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N23" s="48">
+      <c r="N23" s="91">
         <v>15</v>
       </c>
-      <c r="O23" s="65" t="s">
+      <c r="O23" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P23" s="51">
+      <c r="P23" s="92">
         <v>6.5600000000000006E-2</v>
       </c>
-      <c r="Q23" s="51">
+      <c r="Q23" s="115">
         <f t="shared" si="2"/>
         <v>0.9840000000000001</v>
       </c>
-      <c r="R23" s="49"/>
-      <c r="S23" s="51"/>
+      <c r="R23" s="91"/>
+      <c r="S23" s="92"/>
     </row>
     <row r="24" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="37">
+      <c r="B24" s="94">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="45" t="s">
         <v>216</v>
       </c>
       <c r="F24" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="46" t="s">
+      <c r="G24" s="45" t="s">
         <v>217</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="46" t="s">
         <v>130</v>
       </c>
       <c r="I24" s="45" t="s">
@@ -2941,110 +3114,110 @@
       <c r="J24" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="K24" s="45" t="s">
+      <c r="K24" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L24" s="45">
         <v>11</v>
       </c>
-      <c r="M24" s="45">
+      <c r="M24" s="46">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="N24" s="45">
         <v>120</v>
       </c>
-      <c r="O24" s="63" t="s">
+      <c r="O24" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P24" s="50">
         <v>4.6100000000000002E-2</v>
       </c>
-      <c r="Q24" s="50">
+      <c r="Q24" s="114">
         <f>P24*N24</f>
         <v>5.532</v>
       </c>
-      <c r="R24" s="46"/>
+      <c r="R24" s="45"/>
       <c r="S24" s="50"/>
     </row>
     <row r="25" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="37">
+      <c r="B25" s="94">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="89" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="49" t="s">
+      <c r="G25" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="H25" s="48" t="s">
+      <c r="H25" s="90" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J25" s="48" t="s">
+      <c r="I25" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="91" t="s">
         <v>150</v>
       </c>
-      <c r="K25" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L25" s="48">
+      <c r="K25" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L25" s="91">
         <v>10</v>
       </c>
-      <c r="M25" s="48">
+      <c r="M25" s="90">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N25" s="48">
+      <c r="N25" s="91">
         <v>105</v>
       </c>
-      <c r="O25" s="65" t="s">
+      <c r="O25" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P25" s="51">
+      <c r="P25" s="92">
         <v>0.25779999999999997</v>
       </c>
-      <c r="Q25" s="51">
+      <c r="Q25" s="115">
         <f t="shared" si="2"/>
         <v>27.068999999999996</v>
       </c>
-      <c r="R25" s="49"/>
-      <c r="S25" s="51"/>
+      <c r="R25" s="91"/>
+      <c r="S25" s="92"/>
     </row>
     <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="37">
+      <c r="B26" s="94">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="45" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="46" t="s">
+      <c r="G26" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="46" t="s">
         <v>132</v>
       </c>
       <c r="I26" s="45" t="s">
@@ -3053,109 +3226,109 @@
       <c r="J26" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="K26" s="45" t="s">
+      <c r="K26" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L26" s="45">
         <v>10</v>
       </c>
-      <c r="M26" s="45">
+      <c r="M26" s="46">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="N26" s="45">
         <v>110</v>
       </c>
-      <c r="O26" s="63" t="s">
+      <c r="O26" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P26" s="50">
         <v>6.7900000000000002E-2</v>
       </c>
-      <c r="Q26" s="50">
+      <c r="Q26" s="114">
         <f t="shared" si="2"/>
         <v>7.4690000000000003</v>
       </c>
-      <c r="R26" s="46"/>
+      <c r="R26" s="45"/>
       <c r="S26" s="50"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="37">
+      <c r="B27" s="94">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="67" t="s">
+      <c r="D27" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="49" t="s">
+      <c r="G27" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="I27" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J27" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="K27" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="48">
+      <c r="H27" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="I27" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="K27" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L27" s="91">
         <v>4</v>
       </c>
-      <c r="M27" s="48">
+      <c r="M27" s="90">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N27" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="O27" s="65" t="s">
-        <v>184</v>
-      </c>
-      <c r="P27" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q27" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="R27" s="49"/>
-      <c r="S27" s="51"/>
+      <c r="N27" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="O27" s="111" t="s">
+        <v>184</v>
+      </c>
+      <c r="P27" s="92" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q27" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="R27" s="91"/>
+      <c r="S27" s="92"/>
     </row>
     <row r="28" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="37">
+      <c r="B28" s="94">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="D28" s="66" t="s">
+      <c r="D28" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="46" t="s">
+      <c r="E28" s="45" t="s">
         <v>66</v>
       </c>
       <c r="F28" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="46" t="s">
+      <c r="G28" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="46" t="s">
         <v>133</v>
       </c>
       <c r="I28" s="45" t="s">
@@ -3164,222 +3337,222 @@
       <c r="J28" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="K28" s="45" t="s">
+      <c r="K28" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L28" s="45">
         <v>1</v>
       </c>
-      <c r="M28" s="45">
+      <c r="M28" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N28" s="45">
         <v>15</v>
       </c>
-      <c r="O28" s="63" t="s">
+      <c r="O28" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P28" s="50">
         <v>6.7400000000000002E-2</v>
       </c>
-      <c r="Q28" s="50">
+      <c r="Q28" s="114">
         <f t="shared" si="2"/>
         <v>1.0110000000000001</v>
       </c>
-      <c r="R28" s="46"/>
+      <c r="R28" s="45"/>
       <c r="S28" s="50"/>
     </row>
     <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="37">
+      <c r="B29" s="94">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="88" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="48" t="s">
+      <c r="F29" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="91" t="s">
         <v>112</v>
       </c>
-      <c r="H29" s="48" t="s">
+      <c r="H29" s="90" t="s">
         <v>134</v>
       </c>
-      <c r="I29" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J29" s="48" t="s">
+      <c r="I29" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="K29" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L29" s="48">
+      <c r="K29" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" s="91">
         <v>1</v>
       </c>
-      <c r="M29" s="48">
+      <c r="M29" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N29" s="48">
+      <c r="N29" s="91">
         <v>50</v>
       </c>
-      <c r="O29" s="65" t="s">
+      <c r="O29" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P29" s="51">
+      <c r="P29" s="92">
         <v>1.47E-2</v>
       </c>
-      <c r="Q29" s="51">
+      <c r="Q29" s="115">
         <f t="shared" si="2"/>
         <v>0.73499999999999999</v>
       </c>
-      <c r="R29" s="49"/>
-      <c r="S29" s="51"/>
+      <c r="R29" s="91"/>
+      <c r="S29" s="92"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="70">
+      <c r="B30" s="105">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="71" t="s">
+      <c r="C30" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="72" t="s">
+      <c r="D30" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="73" t="s">
+      <c r="E30" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="F30" s="74" t="s">
+      <c r="F30" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="71" t="s">
         <v>223</v>
       </c>
-      <c r="H30" s="74" t="s">
+      <c r="H30" s="70" t="s">
         <v>224</v>
       </c>
-      <c r="I30" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="J30" s="74" t="s">
+      <c r="I30" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="J30" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="K30" s="74" t="s">
+      <c r="K30" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="L30" s="74">
+      <c r="L30" s="71">
         <v>6</v>
       </c>
-      <c r="M30" s="74">
+      <c r="M30" s="70">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N30" s="74">
+      <c r="N30" s="71">
         <v>100</v>
       </c>
-      <c r="O30" s="75" t="s">
+      <c r="O30" s="112" t="s">
         <v>193</v>
       </c>
-      <c r="P30" s="76">
+      <c r="P30" s="72">
         <v>1E-3</v>
       </c>
-      <c r="Q30" s="76">
+      <c r="Q30" s="116">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R30" s="73"/>
-      <c r="S30" s="76"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="72"/>
     </row>
     <row r="31" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="37">
+      <c r="B31" s="94">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E31" s="91" t="s">
         <v>232</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="F31" s="91" t="s">
         <v>233</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="91" t="s">
         <v>234</v>
       </c>
-      <c r="H31" s="48" t="s">
+      <c r="H31" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="I31" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J31" s="48" t="s">
+      <c r="I31" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J31" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="K31" s="48" t="s">
+      <c r="K31" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="L31" s="48">
+      <c r="L31" s="91">
         <v>3</v>
       </c>
-      <c r="M31" s="48">
+      <c r="M31" s="90">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N31" s="48">
+      <c r="N31" s="91">
         <v>100</v>
       </c>
-      <c r="O31" s="65" t="s">
+      <c r="O31" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P31" s="51">
+      <c r="P31" s="92">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q31" s="51">
+      <c r="Q31" s="115">
         <f t="shared" si="2"/>
         <v>0.69</v>
       </c>
-      <c r="R31" s="49"/>
-      <c r="S31" s="51"/>
+      <c r="R31" s="91"/>
+      <c r="S31" s="92"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="37">
+      <c r="B32" s="94">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="66" t="s">
+      <c r="D32" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="46" t="s">
+      <c r="E32" s="45" t="s">
         <v>68</v>
       </c>
       <c r="F32" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="46" t="s">
+      <c r="G32" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="H32" s="45" t="s">
+      <c r="H32" s="46" t="s">
         <v>135</v>
       </c>
       <c r="I32" s="45" t="s">
@@ -3388,110 +3561,110 @@
       <c r="J32" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="45" t="s">
+      <c r="K32" s="46" t="s">
         <v>169</v>
       </c>
       <c r="L32" s="45">
         <v>3</v>
       </c>
-      <c r="M32" s="45">
+      <c r="M32" s="46">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="N32" s="45">
         <v>50</v>
       </c>
-      <c r="O32" s="63" t="s">
+      <c r="O32" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P32" s="50">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="Q32" s="50">
+      <c r="Q32" s="114">
         <f t="shared" si="2"/>
         <v>0.38999999999999996</v>
       </c>
-      <c r="R32" s="46"/>
+      <c r="R32" s="45"/>
       <c r="S32" s="50"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="37">
+      <c r="B33" s="94">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="62" t="s">
+      <c r="C33" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="67" t="s">
+      <c r="D33" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="49" t="s">
+      <c r="E33" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="48" t="s">
+      <c r="F33" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="64" t="s">
+      <c r="G33" s="109" t="s">
         <v>114</v>
       </c>
-      <c r="H33" s="48" t="s">
+      <c r="H33" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="I33" s="49" t="s">
+      <c r="I33" s="91" t="s">
         <v>197</v>
       </c>
-      <c r="J33" s="48" t="s">
+      <c r="J33" s="91" t="s">
         <v>196</v>
       </c>
-      <c r="K33" s="48" t="s">
+      <c r="K33" s="90" t="s">
         <v>170</v>
       </c>
-      <c r="L33" s="48">
+      <c r="L33" s="91">
         <v>2</v>
       </c>
-      <c r="M33" s="48">
+      <c r="M33" s="90">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N33" s="48">
+      <c r="N33" s="91">
         <v>100</v>
       </c>
-      <c r="O33" s="65" t="s">
+      <c r="O33" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P33" s="51">
+      <c r="P33" s="92">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q33" s="51">
+      <c r="Q33" s="115">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="R33" s="49"/>
-      <c r="S33" s="51"/>
+      <c r="R33" s="91"/>
+      <c r="S33" s="92"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="37">
+      <c r="B34" s="94">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="66" t="s">
+      <c r="D34" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="46" t="s">
+      <c r="E34" s="45" t="s">
         <v>70</v>
       </c>
       <c r="F34" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="46" t="s">
+      <c r="G34" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="H34" s="45" t="s">
+      <c r="H34" s="46" t="s">
         <v>126</v>
       </c>
       <c r="I34" s="45" t="s">
@@ -3500,110 +3673,110 @@
       <c r="J34" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="K34" s="45" t="s">
+      <c r="K34" s="46" t="s">
         <v>171</v>
       </c>
       <c r="L34" s="45">
         <v>1</v>
       </c>
-      <c r="M34" s="45">
+      <c r="M34" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N34" s="45">
         <v>100</v>
       </c>
-      <c r="O34" s="63" t="s">
+      <c r="O34" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P34" s="50">
         <v>1.4E-3</v>
       </c>
-      <c r="Q34" s="50">
+      <c r="Q34" s="114">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R34" s="46"/>
+      <c r="R34" s="45"/>
       <c r="S34" s="50"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="37">
+      <c r="B35" s="94">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="67" t="s">
+      <c r="D35" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="49" t="s">
+      <c r="E35" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="G35" s="49" t="s">
+      <c r="G35" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="48" t="s">
+      <c r="H35" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="I35" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J35" s="48" t="s">
+      <c r="I35" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="91" t="s">
         <v>198</v>
       </c>
-      <c r="K35" s="48" t="s">
+      <c r="K35" s="90" t="s">
         <v>172</v>
       </c>
-      <c r="L35" s="48">
+      <c r="L35" s="91">
         <v>1</v>
       </c>
-      <c r="M35" s="48">
+      <c r="M35" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N35" s="48">
+      <c r="N35" s="91">
         <v>100</v>
       </c>
-      <c r="O35" s="65" t="s">
+      <c r="O35" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P35" s="51">
+      <c r="P35" s="92">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q35" s="51">
+      <c r="Q35" s="115">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="R35" s="49"/>
-      <c r="S35" s="51"/>
+      <c r="R35" s="91"/>
+      <c r="S35" s="92"/>
     </row>
     <row r="36" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="37">
+      <c r="B36" s="94">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="66" t="s">
+      <c r="D36" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="46" t="s">
+      <c r="E36" s="45" t="s">
         <v>72</v>
       </c>
       <c r="F36" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="46" t="s">
+      <c r="G36" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="H36" s="45" t="s">
+      <c r="H36" s="46" t="s">
         <v>126</v>
       </c>
       <c r="I36" s="45" t="s">
@@ -3612,110 +3785,110 @@
       <c r="J36" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="K36" s="45" t="s">
+      <c r="K36" s="46" t="s">
         <v>173</v>
       </c>
       <c r="L36" s="45">
         <v>10</v>
       </c>
-      <c r="M36" s="45">
+      <c r="M36" s="46">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="N36" s="45">
         <v>200</v>
       </c>
-      <c r="O36" s="63" t="s">
+      <c r="O36" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P36" s="50">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q36" s="50">
+      <c r="Q36" s="114">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R36" s="46"/>
+      <c r="R36" s="45"/>
       <c r="S36" s="50"/>
     </row>
     <row r="37" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="37">
+      <c r="B37" s="94">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="62" t="s">
+      <c r="C37" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="67" t="s">
+      <c r="D37" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="49" t="s">
+      <c r="E37" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="48" t="s">
+      <c r="F37" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="48" t="s">
+      <c r="H37" s="90" t="s">
         <v>136</v>
       </c>
-      <c r="I37" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J37" s="48" t="s">
+      <c r="I37" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="91" t="s">
         <v>156</v>
       </c>
-      <c r="K37" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L37" s="48">
+      <c r="K37" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L37" s="91">
         <v>1</v>
       </c>
-      <c r="M37" s="48">
+      <c r="M37" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N37" s="48">
+      <c r="N37" s="91">
         <v>20</v>
       </c>
-      <c r="O37" s="65" t="s">
+      <c r="O37" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P37" s="51">
+      <c r="P37" s="92">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="Q37" s="51">
+      <c r="Q37" s="115">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
-      <c r="R37" s="49"/>
-      <c r="S37" s="51"/>
+      <c r="R37" s="91"/>
+      <c r="S37" s="92"/>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="37">
+      <c r="B38" s="94">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="66" t="s">
+      <c r="D38" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="45" t="s">
         <v>74</v>
       </c>
       <c r="F38" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="G38" s="46" t="s">
+      <c r="G38" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="46" t="s">
         <v>137</v>
       </c>
       <c r="I38" s="45" t="s">
@@ -3724,110 +3897,110 @@
       <c r="J38" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="K38" s="45" t="s">
+      <c r="K38" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L38" s="45">
         <v>1</v>
       </c>
-      <c r="M38" s="45">
+      <c r="M38" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N38" s="45">
         <v>11</v>
       </c>
-      <c r="O38" s="63" t="s">
+      <c r="O38" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P38" s="50">
         <v>3.3553000000000002</v>
       </c>
-      <c r="Q38" s="50">
+      <c r="Q38" s="114">
         <f t="shared" si="2"/>
         <v>36.908300000000004</v>
       </c>
-      <c r="R38" s="46"/>
+      <c r="R38" s="45"/>
       <c r="S38" s="50"/>
     </row>
     <row r="39" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="37">
+      <c r="B39" s="94">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="67" t="s">
+      <c r="D39" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="49" t="s">
+      <c r="E39" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="48" t="s">
+      <c r="F39" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="G39" s="49" t="s">
+      <c r="G39" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="H39" s="48" t="s">
+      <c r="H39" s="90" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J39" s="48" t="s">
+      <c r="I39" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J39" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="K39" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L39" s="48">
+      <c r="K39" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L39" s="91">
         <v>1</v>
       </c>
-      <c r="M39" s="48">
+      <c r="M39" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N39" s="48">
+      <c r="N39" s="91">
         <v>11</v>
       </c>
-      <c r="O39" s="65" t="s">
+      <c r="O39" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P39" s="51">
+      <c r="P39" s="92">
         <v>0.70960000000000001</v>
       </c>
-      <c r="Q39" s="51">
+      <c r="Q39" s="115">
         <f t="shared" si="2"/>
         <v>7.8056000000000001</v>
       </c>
-      <c r="R39" s="49"/>
-      <c r="S39" s="51"/>
+      <c r="R39" s="91"/>
+      <c r="S39" s="92"/>
     </row>
     <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="37">
+      <c r="B40" s="94">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="66" t="s">
+      <c r="D40" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="E40" s="46" t="s">
+      <c r="E40" s="45" t="s">
         <v>76</v>
       </c>
       <c r="F40" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="G40" s="46" t="s">
+      <c r="G40" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="H40" s="45" t="s">
+      <c r="H40" s="46" t="s">
         <v>139</v>
       </c>
       <c r="I40" s="45" t="s">
@@ -3836,110 +4009,110 @@
       <c r="J40" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="K40" s="45" t="s">
+      <c r="K40" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L40" s="45">
         <v>10</v>
       </c>
-      <c r="M40" s="45">
+      <c r="M40" s="46">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="N40" s="45">
         <v>105</v>
       </c>
-      <c r="O40" s="63" t="s">
+      <c r="O40" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P40" s="50">
         <v>0.11749999999999999</v>
       </c>
-      <c r="Q40" s="50">
+      <c r="Q40" s="114">
         <f t="shared" si="2"/>
         <v>12.337499999999999</v>
       </c>
-      <c r="R40" s="46"/>
+      <c r="R40" s="45"/>
       <c r="S40" s="50"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="37">
+      <c r="B41" s="94">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="62" t="s">
+      <c r="C41" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="67" t="s">
+      <c r="D41" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="49" t="s">
+      <c r="E41" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="F41" s="91" t="s">
         <v>97</v>
       </c>
-      <c r="G41" s="49" t="s">
+      <c r="G41" s="91" t="s">
         <v>121</v>
       </c>
-      <c r="H41" s="48" t="s">
+      <c r="H41" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="I41" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="J41" s="48" t="s">
+      <c r="I41" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J41" s="91" t="s">
         <v>160</v>
       </c>
-      <c r="K41" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="L41" s="48">
+      <c r="K41" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L41" s="91">
         <v>1</v>
       </c>
-      <c r="M41" s="48">
+      <c r="M41" s="90">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N41" s="48">
+      <c r="N41" s="91">
         <v>15</v>
       </c>
-      <c r="O41" s="65" t="s">
+      <c r="O41" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="P41" s="51">
+      <c r="P41" s="92">
         <v>0.3513</v>
       </c>
-      <c r="Q41" s="51">
+      <c r="Q41" s="115">
         <f t="shared" si="2"/>
         <v>5.2694999999999999</v>
       </c>
-      <c r="R41" s="49"/>
-      <c r="S41" s="51"/>
+      <c r="R41" s="91"/>
+      <c r="S41" s="92"/>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="37">
+      <c r="B42" s="94">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="66" t="s">
+      <c r="D42" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="E42" s="46" t="s">
+      <c r="E42" s="45" t="s">
         <v>78</v>
       </c>
       <c r="F42" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="G42" s="46" t="s">
+      <c r="G42" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="H42" s="46" t="s">
         <v>200</v>
       </c>
       <c r="I42" s="45" t="s">
@@ -3948,133 +4121,363 @@
       <c r="J42" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="K42" s="45" t="s">
+      <c r="K42" s="46" t="s">
         <v>184</v>
       </c>
       <c r="L42" s="45">
         <v>2</v>
       </c>
-      <c r="M42" s="45">
+      <c r="M42" s="46">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N42" s="45">
         <v>25</v>
       </c>
-      <c r="O42" s="63" t="s">
+      <c r="O42" s="110" t="s">
         <v>193</v>
       </c>
       <c r="P42" s="50">
         <v>8.1199999999999994E-2</v>
       </c>
-      <c r="Q42" s="50">
+      <c r="Q42" s="114">
         <f t="shared" si="2"/>
         <v>2.0299999999999998</v>
       </c>
-      <c r="R42" s="46"/>
+      <c r="R42" s="45"/>
       <c r="S42" s="50"/>
     </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="36"/>
-      <c r="N43" s="89" t="s">
+    <row r="43" spans="1:19" s="75" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="73"/>
+      <c r="B43" s="94">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="88" t="s">
+        <v>237</v>
+      </c>
+      <c r="D43" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="91" t="s">
+        <v>241</v>
+      </c>
+      <c r="F43" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="G43" s="91" t="s">
+        <v>238</v>
+      </c>
+      <c r="H43" s="90" t="s">
+        <v>130</v>
+      </c>
+      <c r="I43" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J43" s="91" t="s">
+        <v>239</v>
+      </c>
+      <c r="K43" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L43" s="91">
+        <v>11</v>
+      </c>
+      <c r="M43" s="90">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="N43" s="91">
+        <v>115</v>
+      </c>
+      <c r="O43" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="P43" s="92">
+        <v>0.1517</v>
+      </c>
+      <c r="Q43" s="115">
+        <f t="shared" si="2"/>
+        <v>17.445499999999999</v>
+      </c>
+      <c r="R43" s="91"/>
+      <c r="S43" s="92"/>
+    </row>
+    <row r="44" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="94">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="88" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" s="91" t="s">
+        <v>242</v>
+      </c>
+      <c r="F44" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="G44" s="91" t="s">
+        <v>240</v>
+      </c>
+      <c r="H44" s="90" t="s">
+        <v>243</v>
+      </c>
+      <c r="I44" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J44" s="91" t="s">
+        <v>244</v>
+      </c>
+      <c r="K44" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L44" s="91">
+        <v>1</v>
+      </c>
+      <c r="M44" s="90">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N44" s="91">
+        <v>15</v>
+      </c>
+      <c r="O44" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="P44" s="92">
+        <v>0.34610000000000002</v>
+      </c>
+      <c r="Q44" s="115">
+        <f t="shared" si="2"/>
+        <v>5.1915000000000004</v>
+      </c>
+      <c r="R44" s="91"/>
+      <c r="S44" s="92"/>
+    </row>
+    <row r="45" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="94">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="88" t="s">
+        <v>237</v>
+      </c>
+      <c r="D45" s="89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="91" t="s">
+        <v>248</v>
+      </c>
+      <c r="F45" s="91" t="s">
+        <v>185</v>
+      </c>
+      <c r="G45" s="91" t="s">
+        <v>245</v>
+      </c>
+      <c r="H45" s="90" t="s">
+        <v>249</v>
+      </c>
+      <c r="I45" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J45" s="91" t="s">
+        <v>252</v>
+      </c>
+      <c r="K45" s="90" t="s">
+        <v>184</v>
+      </c>
+      <c r="L45" s="91">
+        <v>1</v>
+      </c>
+      <c r="M45" s="90">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N45" s="91">
+        <v>11</v>
+      </c>
+      <c r="O45" s="111" t="s">
+        <v>193</v>
+      </c>
+      <c r="P45" s="92">
+        <v>0.68320000000000003</v>
+      </c>
+      <c r="Q45" s="115">
+        <f t="shared" si="2"/>
+        <v>7.5152000000000001</v>
+      </c>
+      <c r="R45" s="91"/>
+      <c r="S45" s="92"/>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B46" s="94">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="106" t="s">
+        <v>237</v>
+      </c>
+      <c r="D46" s="107" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" s="108" t="s">
+        <v>247</v>
+      </c>
+      <c r="F46" s="108" t="s">
+        <v>185</v>
+      </c>
+      <c r="G46" s="108" t="s">
+        <v>246</v>
+      </c>
+      <c r="H46" s="118" t="s">
+        <v>250</v>
+      </c>
+      <c r="I46" s="108" t="s">
+        <v>184</v>
+      </c>
+      <c r="J46" s="108" t="s">
+        <v>251</v>
+      </c>
+      <c r="K46" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="L46" s="108">
+        <v>1</v>
+      </c>
+      <c r="M46" s="118">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N46" s="108">
+        <v>11</v>
+      </c>
+      <c r="O46" s="119" t="s">
+        <v>193</v>
+      </c>
+      <c r="P46" s="113">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="Q46" s="120">
+        <f t="shared" si="2"/>
+        <v>10.571</v>
+      </c>
+      <c r="R46" s="108"/>
+      <c r="S46" s="113"/>
+    </row>
+    <row r="47" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="95"/>
+      <c r="D47" s="96"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="98"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="98"/>
+      <c r="I47" s="99"/>
+      <c r="J47" s="98"/>
+      <c r="K47" s="99"/>
+      <c r="L47" s="99"/>
+      <c r="M47" s="99"/>
+      <c r="N47" s="100" t="s">
         <v>220</v>
       </c>
-      <c r="O43" s="90"/>
-      <c r="P43" s="90"/>
-      <c r="Q43" s="68">
-        <f>SUM(Q10:Q42)</f>
-        <v>120.3629</v>
-      </c>
-      <c r="R43" s="85"/>
-      <c r="S43" s="86"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="89" t="s">
+      <c r="O47" s="101"/>
+      <c r="P47" s="101"/>
+      <c r="Q47" s="102">
+        <f>SUM(Q10:Q46)</f>
+        <v>161.08609999999999</v>
+      </c>
+      <c r="R47" s="103"/>
+      <c r="S47" s="104"/>
+    </row>
+    <row r="48" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="85" t="s">
         <v>221</v>
       </c>
-      <c r="O44" s="90"/>
-      <c r="P44" s="90"/>
-      <c r="Q44" s="69">
-        <f>Q43/10</f>
-        <v>12.036289999999999</v>
-      </c>
-      <c r="R44" s="87"/>
-      <c r="S44" s="88"/>
+      <c r="O48" s="86"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="67">
+        <f>Q47/10</f>
+        <v>16.108609999999999</v>
+      </c>
+      <c r="R48" s="83"/>
+      <c r="S48" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R43:S44"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R47:S48"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="N48:P48"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{B4B92583-AFC5-4C70-B0C5-E1A2E39FC483}"/>
-    <hyperlink ref="O12" r:id="rId2" xr:uid="{02F1C72C-646B-4E69-843C-7B79512658BB}"/>
-    <hyperlink ref="O13" r:id="rId3" xr:uid="{9C8DE64B-39DC-4FA5-BC82-70A9347B5CB7}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{B57C6DE4-F114-47CC-A4AE-81250E951A85}"/>
-    <hyperlink ref="O16" r:id="rId5" xr:uid="{1033A83E-EF73-44FE-BC7E-01798A863B28}"/>
-    <hyperlink ref="O20" r:id="rId6" xr:uid="{D31CF805-77DA-485C-A79F-60E569C18A2B}"/>
-    <hyperlink ref="O22" r:id="rId7" xr:uid="{2FA3E246-B558-4663-817E-A113191AF2F4}"/>
-    <hyperlink ref="O26" r:id="rId8" xr:uid="{021899FA-497D-462B-A309-42059B1C785F}"/>
-    <hyperlink ref="O28" r:id="rId9" xr:uid="{FEA5DC77-A5A9-4599-B4FE-89EA64A3C261}"/>
-    <hyperlink ref="O29" r:id="rId10" xr:uid="{C6504500-546C-423F-893B-28D6DA42E4F7}"/>
-    <hyperlink ref="O32" r:id="rId11" xr:uid="{C8130DAA-34AE-4E20-9121-7EC1F059B813}"/>
-    <hyperlink ref="O33" r:id="rId12" xr:uid="{0760B43C-F473-4C7B-9BB2-B4785A54B864}"/>
-    <hyperlink ref="O34" r:id="rId13" xr:uid="{80365478-7D4F-4298-B8A0-5B830250FF7F}"/>
-    <hyperlink ref="O35" r:id="rId14" xr:uid="{2F15CACC-E877-400C-AF8C-6D941C0E9E1A}"/>
-    <hyperlink ref="O36" r:id="rId15" xr:uid="{177304F5-C295-47FB-961B-5E3A1E1C4732}"/>
-    <hyperlink ref="O37" r:id="rId16" xr:uid="{6F70ADEF-E864-4D13-91BC-C9E9488F0F32}"/>
-    <hyperlink ref="O38" r:id="rId17" xr:uid="{58C7DEB9-7ECA-44CE-9BFE-5A219FC559C1}"/>
-    <hyperlink ref="O39" r:id="rId18" xr:uid="{C7EE6E03-4AEB-4816-8A0A-BB0E31CFBA87}"/>
-    <hyperlink ref="O40" r:id="rId19" xr:uid="{EAA21C97-CD09-4516-AB51-2716850C59BA}"/>
-    <hyperlink ref="O41" r:id="rId20" xr:uid="{950C4C9C-339D-4300-B792-F7567D466B6D}"/>
-    <hyperlink ref="O42" r:id="rId21" xr:uid="{0F21039F-6B3C-4119-AC4F-06AA73524D9A}"/>
-    <hyperlink ref="O25" r:id="rId22" xr:uid="{805F7ACB-D787-441E-A591-2AE7335E81B1}"/>
-    <hyperlink ref="O19" r:id="rId23" xr:uid="{C6D95856-76AF-4CFB-A4FB-A06F479B4719}"/>
-    <hyperlink ref="O17" r:id="rId24" xr:uid="{43FDAEFF-6403-40D1-9C4E-7D1D36A4547B}"/>
-    <hyperlink ref="O18" r:id="rId25" xr:uid="{139A5CC0-C786-4F85-AA66-3AEE409EB113}"/>
-    <hyperlink ref="O21" r:id="rId26" xr:uid="{8C8DA922-14BF-412F-BFF6-B7E698A6F7FE}"/>
-    <hyperlink ref="O23" r:id="rId27" xr:uid="{8F538101-09B9-4F97-96DB-04960D66F6EE}"/>
-    <hyperlink ref="O24" r:id="rId28" xr:uid="{9A904CE7-14A6-4D9E-9A55-CB2910411196}"/>
-    <hyperlink ref="O30" r:id="rId29" xr:uid="{AA1C896D-0A54-4267-B8EF-A8CBFBFDAF8E}"/>
-    <hyperlink ref="O11" r:id="rId30" xr:uid="{06B3400B-70EE-41D2-9AFA-71E148298236}"/>
-    <hyperlink ref="O31" r:id="rId31" xr:uid="{9DDFFD2D-F6D3-4F9D-B54D-1FC61840F009}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O20" r:id="rId6"/>
+    <hyperlink ref="O22" r:id="rId7"/>
+    <hyperlink ref="O26" r:id="rId8"/>
+    <hyperlink ref="O28" r:id="rId9"/>
+    <hyperlink ref="O29" r:id="rId10"/>
+    <hyperlink ref="O32" r:id="rId11"/>
+    <hyperlink ref="O33" r:id="rId12"/>
+    <hyperlink ref="O34" r:id="rId13"/>
+    <hyperlink ref="O35" r:id="rId14"/>
+    <hyperlink ref="O36" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O39" r:id="rId18"/>
+    <hyperlink ref="O40" r:id="rId19"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O42" r:id="rId21"/>
+    <hyperlink ref="O25" r:id="rId22"/>
+    <hyperlink ref="O19" r:id="rId23"/>
+    <hyperlink ref="O17" r:id="rId24"/>
+    <hyperlink ref="O18" r:id="rId25"/>
+    <hyperlink ref="O21" r:id="rId26"/>
+    <hyperlink ref="O23" r:id="rId27"/>
+    <hyperlink ref="O24" r:id="rId28"/>
+    <hyperlink ref="O30" r:id="rId29"/>
+    <hyperlink ref="O11" r:id="rId30"/>
+    <hyperlink ref="O31" r:id="rId31"/>
+    <hyperlink ref="O43" r:id="rId32"/>
+    <hyperlink ref="O44" r:id="rId33"/>
+    <hyperlink ref="O45" r:id="rId34"/>
+    <hyperlink ref="O46" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
-  <drawing r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
+  <drawing r:id="rId37"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0695B8-3988-408E-B7A3-E10795A47168}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4108,15 +4511,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="82"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4126,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="53" t="s">
         <v>186</v>
       </c>
       <c r="G2" s="12"/>
@@ -4151,7 +4554,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="54" t="s">
         <v>187</v>
       </c>
       <c r="G3" s="13"/>
@@ -4166,7 +4569,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="83"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4176,7 +4579,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="57" t="s">
+      <c r="F4" s="55" t="s">
         <v>187</v>
       </c>
       <c r="G4" s="14"/>
@@ -4191,7 +4594,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="84"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4201,7 +4604,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -4216,7 +4619,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="84"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4237,7 +4640,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="84"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4258,7 +4661,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="84"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4279,7 +4682,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="84"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4310,13 +4713,13 @@
       <c r="J9" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="K9" s="59" t="s">
+      <c r="K9" s="57" t="s">
         <v>176</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="M9" s="60" t="s">
+      <c r="M9" s="58" t="s">
         <v>228</v>
       </c>
       <c r="N9" s="31" t="s">
@@ -4338,16 +4741,16 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="77"/>
+    <row r="10" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="73"/>
       <c r="B10" s="37">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="64" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="46" t="s">
@@ -4381,7 +4784,7 @@
       <c r="N10" s="45">
         <v>2060</v>
       </c>
-      <c r="O10" s="63" t="s">
+      <c r="O10" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P10" s="50">
@@ -4392,18 +4795,18 @@
         <v>29.252000000000002</v>
       </c>
       <c r="R10" s="46"/>
-      <c r="S10" s="78"/>
-    </row>
-    <row r="11" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="77"/>
+      <c r="S10" s="74"/>
+    </row>
+    <row r="11" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="73"/>
       <c r="B11" s="37">
         <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="65" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="49" t="s">
@@ -4412,7 +4815,7 @@
       <c r="F11" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="62" t="s">
         <v>101</v>
       </c>
       <c r="H11" s="48" t="s">
@@ -4437,7 +4840,7 @@
       <c r="N11" s="48">
         <v>3100</v>
       </c>
-      <c r="O11" s="65" t="s">
+      <c r="O11" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P11" s="51">
@@ -4448,18 +4851,18 @@
         <v>6.2</v>
       </c>
       <c r="R11" s="49"/>
-      <c r="S11" s="80"/>
-    </row>
-    <row r="12" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
+      <c r="S11" s="76"/>
+    </row>
+    <row r="12" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="73"/>
       <c r="B12" s="37">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="64" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="46" t="s">
@@ -4493,7 +4896,7 @@
       <c r="N12" s="45">
         <v>1100</v>
       </c>
-      <c r="O12" s="63" t="s">
+      <c r="O12" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P12" s="50">
@@ -4506,16 +4909,16 @@
       <c r="R12" s="46"/>
       <c r="S12" s="50"/>
     </row>
-    <row r="13" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77"/>
+    <row r="13" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="73"/>
       <c r="B13" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="62" t="s">
+      <c r="C13" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="65" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="49" t="s">
@@ -4524,7 +4927,7 @@
       <c r="F13" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="62" t="s">
         <v>103</v>
       </c>
       <c r="H13" s="48" t="s">
@@ -4549,7 +4952,7 @@
       <c r="N13" s="48">
         <v>1060</v>
       </c>
-      <c r="O13" s="65" t="s">
+      <c r="O13" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P13" s="51">
@@ -4562,16 +4965,16 @@
       <c r="R13" s="49"/>
       <c r="S13" s="51"/>
     </row>
-    <row r="14" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="77"/>
+    <row r="14" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="73"/>
       <c r="B14" s="37">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="66" t="s">
+      <c r="D14" s="64" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="46" t="s">
@@ -4605,7 +5008,7 @@
       <c r="N14" s="45">
         <v>1050</v>
       </c>
-      <c r="O14" s="63" t="s">
+      <c r="O14" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P14" s="50">
@@ -4618,16 +5021,16 @@
       <c r="R14" s="46"/>
       <c r="S14" s="50"/>
     </row>
-    <row r="15" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="77"/>
+    <row r="15" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="73"/>
       <c r="B15" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="62" t="s">
+      <c r="C15" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="65" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="49" t="s">
@@ -4677,16 +5080,16 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="77"/>
+    <row r="16" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="73"/>
       <c r="B16" s="37">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="66" t="s">
+      <c r="D16" s="64" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="46" t="s">
@@ -4720,7 +5123,7 @@
       <c r="N16" s="45">
         <v>1100</v>
       </c>
-      <c r="O16" s="63" t="s">
+      <c r="O16" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P16" s="50">
@@ -4733,16 +5136,16 @@
       <c r="R16" s="46"/>
       <c r="S16" s="50"/>
     </row>
-    <row r="17" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="77"/>
+    <row r="17" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="73"/>
       <c r="B17" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="67" t="s">
+      <c r="D17" s="65" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="49" t="s">
@@ -4776,7 +5179,7 @@
       <c r="N17" s="48">
         <v>1050</v>
       </c>
-      <c r="O17" s="65" t="s">
+      <c r="O17" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P17" s="51">
@@ -4789,16 +5192,16 @@
       <c r="R17" s="49"/>
       <c r="S17" s="51"/>
     </row>
-    <row r="18" spans="1:19" s="79" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="77"/>
+    <row r="18" spans="1:19" s="75" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="73"/>
       <c r="B18" s="37">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="66" t="s">
+      <c r="D18" s="64" t="s">
         <v>202</v>
       </c>
       <c r="E18" s="46" t="s">
@@ -4832,7 +5235,7 @@
       <c r="N18" s="45">
         <v>2060</v>
       </c>
-      <c r="O18" s="63" t="s">
+      <c r="O18" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P18" s="50">
@@ -4845,16 +5248,16 @@
       <c r="R18" s="46"/>
       <c r="S18" s="50"/>
     </row>
-    <row r="19" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="77"/>
+    <row r="19" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="73"/>
       <c r="B19" s="37">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="67" t="s">
+      <c r="D19" s="65" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="49" t="s">
@@ -4888,7 +5291,7 @@
       <c r="N19" s="48">
         <v>1050</v>
       </c>
-      <c r="O19" s="65" t="s">
+      <c r="O19" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P19" s="51">
@@ -4901,16 +5304,16 @@
       <c r="R19" s="49"/>
       <c r="S19" s="51"/>
     </row>
-    <row r="20" spans="1:19" s="79" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="77"/>
+    <row r="20" spans="1:19" s="75" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="73"/>
       <c r="B20" s="37">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="66" t="s">
+      <c r="D20" s="64" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="46" t="s">
@@ -4944,7 +5347,7 @@
       <c r="N20" s="45">
         <v>1050</v>
       </c>
-      <c r="O20" s="63" t="s">
+      <c r="O20" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P20" s="50">
@@ -4957,16 +5360,16 @@
       <c r="R20" s="46"/>
       <c r="S20" s="50"/>
     </row>
-    <row r="21" spans="1:19" s="79" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="77"/>
+    <row r="21" spans="1:19" s="75" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="73"/>
       <c r="B21" s="37">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="D21" s="67" t="s">
+      <c r="D21" s="65" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="49" t="s">
@@ -5000,7 +5403,7 @@
       <c r="N21" s="48">
         <v>1020</v>
       </c>
-      <c r="O21" s="65" t="s">
+      <c r="O21" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P21" s="51">
@@ -5013,16 +5416,16 @@
       <c r="R21" s="49"/>
       <c r="S21" s="51"/>
     </row>
-    <row r="22" spans="1:19" s="79" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="77"/>
+    <row r="22" spans="1:19" s="75" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="73"/>
       <c r="B22" s="37">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="61" t="s">
+      <c r="C22" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D22" s="66" t="s">
+      <c r="D22" s="64" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="46" t="s">
@@ -5056,7 +5459,7 @@
       <c r="N22" s="45">
         <v>1050</v>
       </c>
-      <c r="O22" s="63" t="s">
+      <c r="O22" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P22" s="50">
@@ -5069,16 +5472,16 @@
       <c r="R22" s="46"/>
       <c r="S22" s="50"/>
     </row>
-    <row r="23" spans="1:19" s="79" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="77"/>
+    <row r="23" spans="1:19" s="75" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="73"/>
       <c r="B23" s="37">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="62" t="s">
+      <c r="C23" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="67" t="s">
+      <c r="D23" s="65" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="49" t="s">
@@ -5112,7 +5515,7 @@
       <c r="N23" s="48">
         <v>1050</v>
       </c>
-      <c r="O23" s="65" t="s">
+      <c r="O23" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P23" s="51">
@@ -5125,16 +5528,16 @@
       <c r="R23" s="49"/>
       <c r="S23" s="51"/>
     </row>
-    <row r="24" spans="1:19" s="79" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="77"/>
+    <row r="24" spans="1:19" s="75" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="73"/>
       <c r="B24" s="37">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E24" s="46" t="s">
@@ -5168,7 +5571,7 @@
       <c r="N24" s="45">
         <v>11100</v>
       </c>
-      <c r="O24" s="63" t="s">
+      <c r="O24" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P24" s="50">
@@ -5181,16 +5584,16 @@
       <c r="R24" s="46"/>
       <c r="S24" s="50"/>
     </row>
-    <row r="25" spans="1:19" s="79" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="77"/>
+    <row r="25" spans="1:19" s="75" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
       <c r="B25" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="65" t="s">
         <v>33</v>
       </c>
       <c r="E25" s="49" t="s">
@@ -5224,7 +5627,7 @@
       <c r="N25" s="48">
         <v>10100</v>
       </c>
-      <c r="O25" s="65" t="s">
+      <c r="O25" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P25" s="51">
@@ -5237,16 +5640,16 @@
       <c r="R25" s="49"/>
       <c r="S25" s="51"/>
     </row>
-    <row r="26" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="77"/>
+    <row r="26" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="73"/>
       <c r="B26" s="37">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="64" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="46" t="s">
@@ -5280,7 +5683,7 @@
       <c r="N26" s="45">
         <v>10100</v>
       </c>
-      <c r="O26" s="63" t="s">
+      <c r="O26" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P26" s="50">
@@ -5293,16 +5696,16 @@
       <c r="R26" s="46"/>
       <c r="S26" s="50"/>
     </row>
-    <row r="27" spans="1:19" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="77"/>
+    <row r="27" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="73"/>
       <c r="B27" s="37">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="67" t="s">
+      <c r="D27" s="65" t="s">
         <v>35</v>
       </c>
       <c r="E27" s="49" t="s">
@@ -5336,7 +5739,7 @@
       <c r="N27" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="O27" s="65" t="s">
+      <c r="O27" s="63" t="s">
         <v>184</v>
       </c>
       <c r="P27" s="51" t="s">
@@ -5348,16 +5751,16 @@
       <c r="R27" s="49"/>
       <c r="S27" s="51"/>
     </row>
-    <row r="28" spans="1:19" s="79" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="77"/>
+    <row r="28" spans="1:19" s="75" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="73"/>
       <c r="B28" s="37">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="D28" s="66" t="s">
+      <c r="D28" s="64" t="s">
         <v>36</v>
       </c>
       <c r="E28" s="46" t="s">
@@ -5391,7 +5794,7 @@
       <c r="N28" s="45">
         <v>1050</v>
       </c>
-      <c r="O28" s="63" t="s">
+      <c r="O28" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P28" s="50">
@@ -5404,16 +5807,16 @@
       <c r="R28" s="46"/>
       <c r="S28" s="50"/>
     </row>
-    <row r="29" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="77"/>
+    <row r="29" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="73"/>
       <c r="B29" s="37">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="67" t="s">
+      <c r="D29" s="65" t="s">
         <v>37</v>
       </c>
       <c r="E29" s="49" t="s">
@@ -5447,7 +5850,7 @@
       <c r="N29" s="48">
         <v>1050</v>
       </c>
-      <c r="O29" s="65" t="s">
+      <c r="O29" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P29" s="51">
@@ -5460,16 +5863,16 @@
       <c r="R29" s="49"/>
       <c r="S29" s="51"/>
     </row>
-    <row r="30" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="77"/>
+    <row r="30" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="73"/>
       <c r="B30" s="37">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="66" t="s">
+      <c r="D30" s="64" t="s">
         <v>38</v>
       </c>
       <c r="E30" s="46" t="s">
@@ -5503,7 +5906,7 @@
       <c r="N30" s="45">
         <v>6100</v>
       </c>
-      <c r="O30" s="63" t="s">
+      <c r="O30" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P30" s="50">
@@ -5516,13 +5919,13 @@
       <c r="R30" s="46"/>
       <c r="S30" s="50"/>
     </row>
-    <row r="31" spans="1:19" s="79" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="77"/>
+    <row r="31" spans="1:19" s="75" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="73"/>
       <c r="B31" s="37">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="62" t="s">
+      <c r="C31" s="60" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="48" t="s">
@@ -5559,7 +5962,7 @@
       <c r="N31" s="48">
         <v>3100</v>
       </c>
-      <c r="O31" s="65" t="s">
+      <c r="O31" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P31" s="51">
@@ -5572,16 +5975,16 @@
       <c r="R31" s="49"/>
       <c r="S31" s="51"/>
     </row>
-    <row r="32" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="77"/>
+    <row r="32" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="73"/>
       <c r="B32" s="37">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="66" t="s">
+      <c r="D32" s="64" t="s">
         <v>40</v>
       </c>
       <c r="E32" s="46" t="s">
@@ -5615,7 +6018,7 @@
       <c r="N32" s="45">
         <v>3050</v>
       </c>
-      <c r="O32" s="63" t="s">
+      <c r="O32" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P32" s="50">
@@ -5628,16 +6031,16 @@
       <c r="R32" s="46"/>
       <c r="S32" s="50"/>
     </row>
-    <row r="33" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="77"/>
+    <row r="33" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="73"/>
       <c r="B33" s="37">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="62" t="s">
+      <c r="C33" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="67" t="s">
+      <c r="D33" s="65" t="s">
         <v>41</v>
       </c>
       <c r="E33" s="49" t="s">
@@ -5646,7 +6049,7 @@
       <c r="F33" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="64" t="s">
+      <c r="G33" s="62" t="s">
         <v>114</v>
       </c>
       <c r="H33" s="48" t="s">
@@ -5671,7 +6074,7 @@
       <c r="N33" s="48">
         <v>2100</v>
       </c>
-      <c r="O33" s="65" t="s">
+      <c r="O33" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P33" s="51">
@@ -5684,16 +6087,16 @@
       <c r="R33" s="49"/>
       <c r="S33" s="51"/>
     </row>
-    <row r="34" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="77"/>
+    <row r="34" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="73"/>
       <c r="B34" s="37">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="66" t="s">
+      <c r="D34" s="64" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="46" t="s">
@@ -5727,7 +6130,7 @@
       <c r="N34" s="45">
         <v>1100</v>
       </c>
-      <c r="O34" s="63" t="s">
+      <c r="O34" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P34" s="50">
@@ -5740,16 +6143,16 @@
       <c r="R34" s="46"/>
       <c r="S34" s="50"/>
     </row>
-    <row r="35" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="77"/>
+    <row r="35" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="73"/>
       <c r="B35" s="37">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="67" t="s">
+      <c r="D35" s="65" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="49" t="s">
@@ -5783,7 +6186,7 @@
       <c r="N35" s="48">
         <v>1100</v>
       </c>
-      <c r="O35" s="65" t="s">
+      <c r="O35" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P35" s="51">
@@ -5796,16 +6199,16 @@
       <c r="R35" s="49"/>
       <c r="S35" s="51"/>
     </row>
-    <row r="36" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="77"/>
+    <row r="36" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="73"/>
       <c r="B36" s="37">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="66" t="s">
+      <c r="D36" s="64" t="s">
         <v>44</v>
       </c>
       <c r="E36" s="46" t="s">
@@ -5839,7 +6242,7 @@
       <c r="N36" s="45">
         <v>10100</v>
       </c>
-      <c r="O36" s="63" t="s">
+      <c r="O36" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P36" s="50">
@@ -5852,16 +6255,16 @@
       <c r="R36" s="46"/>
       <c r="S36" s="50"/>
     </row>
-    <row r="37" spans="1:19" s="79" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
+    <row r="37" spans="1:19" s="75" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="73"/>
       <c r="B37" s="37">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="62" t="s">
+      <c r="C37" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="67" t="s">
+      <c r="D37" s="65" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="49" t="s">
@@ -5895,7 +6298,7 @@
       <c r="N37" s="48">
         <v>1080</v>
       </c>
-      <c r="O37" s="65" t="s">
+      <c r="O37" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P37" s="51">
@@ -5908,16 +6311,16 @@
       <c r="R37" s="49"/>
       <c r="S37" s="51"/>
     </row>
-    <row r="38" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="77"/>
+    <row r="38" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="73"/>
       <c r="B38" s="37">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="66" t="s">
+      <c r="D38" s="64" t="s">
         <v>46</v>
       </c>
       <c r="E38" s="46" t="s">
@@ -5951,7 +6354,7 @@
       <c r="N38" s="45">
         <v>1020</v>
       </c>
-      <c r="O38" s="63" t="s">
+      <c r="O38" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P38" s="50">
@@ -5964,16 +6367,16 @@
       <c r="R38" s="46"/>
       <c r="S38" s="50"/>
     </row>
-    <row r="39" spans="1:19" s="79" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="77"/>
+    <row r="39" spans="1:19" s="75" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="73"/>
       <c r="B39" s="37">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="67" t="s">
+      <c r="D39" s="65" t="s">
         <v>47</v>
       </c>
       <c r="E39" s="49" t="s">
@@ -6007,7 +6410,7 @@
       <c r="N39" s="48">
         <v>1020</v>
       </c>
-      <c r="O39" s="65" t="s">
+      <c r="O39" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P39" s="51">
@@ -6020,16 +6423,16 @@
       <c r="R39" s="49"/>
       <c r="S39" s="51"/>
     </row>
-    <row r="40" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="77"/>
+    <row r="40" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="73"/>
       <c r="B40" s="37">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="66" t="s">
+      <c r="D40" s="64" t="s">
         <v>48</v>
       </c>
       <c r="E40" s="46" t="s">
@@ -6063,7 +6466,7 @@
       <c r="N40" s="45">
         <v>10050</v>
       </c>
-      <c r="O40" s="63" t="s">
+      <c r="O40" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P40" s="50">
@@ -6076,16 +6479,16 @@
       <c r="R40" s="46"/>
       <c r="S40" s="50"/>
     </row>
-    <row r="41" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="77"/>
+    <row r="41" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="73"/>
       <c r="B41" s="37">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="62" t="s">
+      <c r="C41" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="67" t="s">
+      <c r="D41" s="65" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="49" t="s">
@@ -6119,7 +6522,7 @@
       <c r="N41" s="48">
         <v>1020</v>
       </c>
-      <c r="O41" s="65" t="s">
+      <c r="O41" s="63" t="s">
         <v>193</v>
       </c>
       <c r="P41" s="51">
@@ -6132,16 +6535,16 @@
       <c r="R41" s="49"/>
       <c r="S41" s="51"/>
     </row>
-    <row r="42" spans="1:19" s="79" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="77"/>
+    <row r="42" spans="1:19" s="75" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="73"/>
       <c r="B42" s="37">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="66" t="s">
+      <c r="D42" s="64" t="s">
         <v>50</v>
       </c>
       <c r="E42" s="46" t="s">
@@ -6175,7 +6578,7 @@
       <c r="N42" s="45">
         <v>20100</v>
       </c>
-      <c r="O42" s="63" t="s">
+      <c r="O42" s="61" t="s">
         <v>193</v>
       </c>
       <c r="P42" s="50">
@@ -6202,17 +6605,17 @@
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
-      <c r="N43" s="89" t="s">
+      <c r="N43" s="85" t="s">
         <v>220</v>
       </c>
-      <c r="O43" s="90"/>
-      <c r="P43" s="90"/>
-      <c r="Q43" s="68">
+      <c r="O43" s="86"/>
+      <c r="P43" s="86"/>
+      <c r="Q43" s="66">
         <f>SUM(Q10:Q42)</f>
         <v>9771.9939999999988</v>
       </c>
-      <c r="R43" s="85"/>
-      <c r="S43" s="86"/>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
     </row>
     <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -6228,17 +6631,17 @@
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
-      <c r="N44" s="89" t="s">
+      <c r="N44" s="85" t="s">
         <v>221</v>
       </c>
-      <c r="O44" s="90"/>
-      <c r="P44" s="90"/>
-      <c r="Q44" s="69">
+      <c r="O44" s="86"/>
+      <c r="P44" s="86"/>
+      <c r="Q44" s="67">
         <f>Q43/1000</f>
         <v>9.7719939999999994</v>
       </c>
-      <c r="R44" s="87"/>
-      <c r="S44" s="88"/>
+      <c r="R44" s="83"/>
+      <c r="S44" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6249,37 +6652,37 @@
     <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{627FB971-793D-4AEF-B47A-C8F9085B4255}"/>
-    <hyperlink ref="O12" r:id="rId2" xr:uid="{CD51F70F-FC04-4BF0-87AF-4C9A8DF950CB}"/>
-    <hyperlink ref="O13" r:id="rId3" xr:uid="{029C345F-A39F-42BE-9D6C-82DC166C9326}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{929FBB15-8077-481E-8177-1F51DC2C88B9}"/>
-    <hyperlink ref="O16" r:id="rId5" xr:uid="{28E1D816-3B09-4FA3-A003-B3F4BDA95F16}"/>
-    <hyperlink ref="O20" r:id="rId6" xr:uid="{BDF8F6EF-26F3-4986-9151-496CC9C1CB3D}"/>
-    <hyperlink ref="O22" r:id="rId7" xr:uid="{40A02C32-5998-4AE6-AE90-3B1499FAC42F}"/>
-    <hyperlink ref="O26" r:id="rId8" xr:uid="{E7E519B9-2C2E-43C0-A3DC-9C1B292187FA}"/>
-    <hyperlink ref="O28" r:id="rId9" xr:uid="{4FC9A57E-AD12-46C2-8B16-410D46B04C70}"/>
-    <hyperlink ref="O29" r:id="rId10" xr:uid="{D3FEDD23-56FF-4B5A-9611-7A5283D26C34}"/>
-    <hyperlink ref="O32" r:id="rId11" xr:uid="{BF12F8F7-9953-4F71-AAB2-3199A66537A2}"/>
-    <hyperlink ref="O33" r:id="rId12" xr:uid="{77D1771E-1D79-4611-86A4-6777949D1505}"/>
-    <hyperlink ref="O34" r:id="rId13" xr:uid="{533CE1F3-C431-460F-87AF-4D119C9D3B0E}"/>
-    <hyperlink ref="O35" r:id="rId14" xr:uid="{6CDA8F3A-56E7-4D3E-BAB4-2E12B2F2979A}"/>
-    <hyperlink ref="O36" r:id="rId15" xr:uid="{4F366CF4-9ECF-45B4-B69D-894A9EF0DFAF}"/>
-    <hyperlink ref="O37" r:id="rId16" xr:uid="{9F05DD87-3575-4F53-9DB7-25856276ED50}"/>
-    <hyperlink ref="O38" r:id="rId17" xr:uid="{32A6BD7D-C270-4A34-8B93-3F6C43507B6D}"/>
-    <hyperlink ref="O39" r:id="rId18" xr:uid="{1687D941-3C59-4F89-B4A7-0DE74F1FC459}"/>
-    <hyperlink ref="O40" r:id="rId19" xr:uid="{2E9A6BFF-C14A-46A4-BDB2-06267D7A9417}"/>
-    <hyperlink ref="O41" r:id="rId20" xr:uid="{91351711-C2B1-49E4-8874-294C8B9F1D3D}"/>
-    <hyperlink ref="O42" r:id="rId21" xr:uid="{E90C19F5-0A1E-4055-9D86-F4A75F07333D}"/>
-    <hyperlink ref="O25" r:id="rId22" xr:uid="{A9CE32FA-D5A3-4588-B571-9CE30C0C3F55}"/>
-    <hyperlink ref="O19" r:id="rId23" xr:uid="{039EB6C6-FF9A-4A7F-8D30-4A60683F606F}"/>
-    <hyperlink ref="O17" r:id="rId24" xr:uid="{7C1D5C80-C028-4564-A760-6D67C3E96266}"/>
-    <hyperlink ref="O18" r:id="rId25" xr:uid="{A669E1B2-8A6D-45B8-B333-ECF6AF131A7D}"/>
-    <hyperlink ref="O21" r:id="rId26" xr:uid="{01E8F6FD-1CA5-4EE5-B51E-73F144886C0A}"/>
-    <hyperlink ref="O23" r:id="rId27" xr:uid="{8B3DEC00-3F2F-4F60-8E68-19574A492D9E}"/>
-    <hyperlink ref="O24" r:id="rId28" xr:uid="{C9352AAE-8A6D-49D9-93A9-49B079080BF8}"/>
-    <hyperlink ref="O30" r:id="rId29" xr:uid="{13FA5982-39ED-422C-A048-6E6582BA3D43}"/>
-    <hyperlink ref="O11" r:id="rId30" xr:uid="{B1B56BA5-9A0B-4338-85D3-01648252D978}"/>
-    <hyperlink ref="O31" r:id="rId31" xr:uid="{1E9702DC-11E0-46A1-8F9B-FC6F12447702}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O20" r:id="rId6"/>
+    <hyperlink ref="O22" r:id="rId7"/>
+    <hyperlink ref="O26" r:id="rId8"/>
+    <hyperlink ref="O28" r:id="rId9"/>
+    <hyperlink ref="O29" r:id="rId10"/>
+    <hyperlink ref="O32" r:id="rId11"/>
+    <hyperlink ref="O33" r:id="rId12"/>
+    <hyperlink ref="O34" r:id="rId13"/>
+    <hyperlink ref="O35" r:id="rId14"/>
+    <hyperlink ref="O36" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O39" r:id="rId18"/>
+    <hyperlink ref="O40" r:id="rId19"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O42" r:id="rId21"/>
+    <hyperlink ref="O25" r:id="rId22"/>
+    <hyperlink ref="O19" r:id="rId23"/>
+    <hyperlink ref="O17" r:id="rId24"/>
+    <hyperlink ref="O18" r:id="rId25"/>
+    <hyperlink ref="O21" r:id="rId26"/>
+    <hyperlink ref="O23" r:id="rId27"/>
+    <hyperlink ref="O24" r:id="rId28"/>
+    <hyperlink ref="O30" r:id="rId29"/>
+    <hyperlink ref="O11" r:id="rId30"/>
+    <hyperlink ref="O31" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId32"/>

--- a/Deliverables/BOM/eSpark_BOM.xlsx
+++ b/Deliverables/BOM/eSpark_BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="256">
   <si>
     <t>Component list</t>
   </si>
@@ -734,9 +734,6 @@
     <t>C12018</t>
   </si>
   <si>
-    <t>Peripheral</t>
-  </si>
-  <si>
     <t>WJ2EDGK-5.08-3P</t>
   </si>
   <si>
@@ -786,6 +783,12 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA Cable </t>
+  </si>
+  <si>
+    <t>Antenna</t>
   </si>
 </sst>
 </file>
@@ -1499,6 +1502,98 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1511,10 +1606,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1522,6 +1617,14 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1531,110 +1634,10 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2067,15 +2070,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="78"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="108"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2086,7 +2089,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="53" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2125,7 +2128,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="79"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2150,7 +2153,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="110"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2175,7 +2178,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="80"/>
+      <c r="S5" s="110"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2196,7 +2199,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="80"/>
+      <c r="S6" s="110"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2217,7 +2220,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="80"/>
+      <c r="S7" s="110"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2238,7 +2241,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="80"/>
+      <c r="S8" s="110"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2299,7 +2302,7 @@
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="94">
+      <c r="B10" s="84">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -2340,78 +2343,78 @@
       <c r="N10" s="45">
         <v>40</v>
       </c>
-      <c r="O10" s="110" t="s">
+      <c r="O10" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P10" s="50">
         <v>2.3900000000000001E-2</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="100">
         <f>P10*N10</f>
         <v>0.95600000000000007</v>
       </c>
       <c r="R10" s="45"/>
-      <c r="S10" s="87"/>
+      <c r="S10" s="77"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="94">
+      <c r="B11" s="84">
         <f t="shared" ref="B11:B46" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="89" t="s">
+      <c r="D11" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="91" t="s">
+      <c r="E11" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="91" t="s">
+      <c r="F11" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="109" t="s">
+      <c r="G11" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="I11" s="91" t="s">
+      <c r="I11" s="81" t="s">
         <v>226</v>
       </c>
-      <c r="J11" s="91" t="s">
+      <c r="J11" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="K11" s="90" t="s">
+      <c r="K11" s="80" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="91">
+      <c r="L11" s="81">
         <v>3</v>
       </c>
-      <c r="M11" s="90">
+      <c r="M11" s="80">
         <f t="shared" ref="M11:M46" si="1">L11*10</f>
         <v>30</v>
       </c>
-      <c r="N11" s="91">
+      <c r="N11" s="81">
         <v>100</v>
       </c>
-      <c r="O11" s="111" t="s">
+      <c r="O11" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P11" s="92">
+      <c r="P11" s="82">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="Q11" s="115">
+      <c r="Q11" s="101">
         <f t="shared" ref="Q11:Q46" si="2">P11*N11</f>
         <v>0.3</v>
       </c>
-      <c r="R11" s="91"/>
-      <c r="S11" s="93"/>
+      <c r="R11" s="81"/>
+      <c r="S11" s="83"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="94">
+      <c r="B12" s="84">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
@@ -2452,13 +2455,13 @@
       <c r="N12" s="45">
         <v>100</v>
       </c>
-      <c r="O12" s="110" t="s">
+      <c r="O12" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P12" s="50">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="Q12" s="114">
+      <c r="Q12" s="100">
         <f t="shared" si="2"/>
         <v>0.45999999999999996</v>
       </c>
@@ -2467,63 +2470,63 @@
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="94">
+      <c r="B13" s="84">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="91" t="s">
+      <c r="E13" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="91" t="s">
+      <c r="F13" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="109" t="s">
+      <c r="G13" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="90" t="s">
+      <c r="H13" s="80" t="s">
         <v>125</v>
       </c>
-      <c r="I13" s="91" t="s">
+      <c r="I13" s="81" t="s">
         <v>194</v>
       </c>
-      <c r="J13" s="91" t="s">
+      <c r="J13" s="81" t="s">
         <v>195</v>
       </c>
-      <c r="K13" s="90" t="s">
+      <c r="K13" s="80" t="s">
         <v>164</v>
       </c>
-      <c r="L13" s="91">
+      <c r="L13" s="81">
         <v>1</v>
       </c>
-      <c r="M13" s="90">
+      <c r="M13" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N13" s="91">
+      <c r="N13" s="81">
         <v>20</v>
       </c>
-      <c r="O13" s="111" t="s">
+      <c r="O13" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P13" s="92">
+      <c r="P13" s="82">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="Q13" s="115">
+      <c r="Q13" s="101">
         <f t="shared" si="2"/>
         <v>0.46800000000000003</v>
       </c>
-      <c r="R13" s="91"/>
-      <c r="S13" s="92"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="82"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="94">
+      <c r="B14" s="84">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
@@ -2564,13 +2567,13 @@
       <c r="N14" s="45">
         <v>50</v>
       </c>
-      <c r="O14" s="110" t="s">
+      <c r="O14" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P14" s="50">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="Q14" s="114">
+      <c r="Q14" s="100">
         <f t="shared" si="2"/>
         <v>0.77999999999999992</v>
       </c>
@@ -2579,66 +2582,66 @@
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="94">
+      <c r="B15" s="84">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="88" t="s">
+      <c r="C15" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="89" t="s">
+      <c r="D15" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="91" t="s">
+      <c r="E15" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="91" t="s">
+      <c r="F15" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="H15" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="I15" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J15" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="K15" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L15" s="91">
+      <c r="G15" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="I15" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="K15" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L15" s="81">
         <v>2</v>
       </c>
-      <c r="M15" s="90">
+      <c r="M15" s="80">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N15" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="O15" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="P15" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q15" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="R15" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="S15" s="91" t="s">
+      <c r="N15" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="O15" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q15" s="101" t="s">
+        <v>184</v>
+      </c>
+      <c r="R15" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="S15" s="81" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="94">
+      <c r="B16" s="84">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
@@ -2679,13 +2682,13 @@
       <c r="N16" s="45">
         <v>100</v>
       </c>
-      <c r="O16" s="110" t="s">
+      <c r="O16" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P16" s="50">
         <v>2E-3</v>
       </c>
-      <c r="Q16" s="114">
+      <c r="Q16" s="100">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
@@ -2694,63 +2697,63 @@
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="94">
+      <c r="B17" s="84">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="88" t="s">
+      <c r="C17" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="89" t="s">
+      <c r="D17" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="91" t="s">
+      <c r="E17" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="91" t="s">
+      <c r="F17" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="91" t="s">
+      <c r="G17" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="90" t="s">
+      <c r="H17" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J17" s="91" t="s">
+      <c r="I17" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J17" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="K17" s="90" t="s">
+      <c r="K17" s="80" t="s">
         <v>166</v>
       </c>
-      <c r="L17" s="91">
+      <c r="L17" s="81">
         <v>1</v>
       </c>
-      <c r="M17" s="90">
+      <c r="M17" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N17" s="91">
+      <c r="N17" s="81">
         <v>50</v>
       </c>
-      <c r="O17" s="111" t="s">
+      <c r="O17" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P17" s="92">
+      <c r="P17" s="82">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="Q17" s="115">
+      <c r="Q17" s="101">
         <f t="shared" si="2"/>
         <v>0.69499999999999995</v>
       </c>
-      <c r="R17" s="91"/>
-      <c r="S17" s="92"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="82"/>
     </row>
     <row r="18" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="94">
+      <c r="B18" s="84">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
@@ -2791,13 +2794,13 @@
       <c r="N18" s="45">
         <v>40</v>
       </c>
-      <c r="O18" s="110" t="s">
+      <c r="O18" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P18" s="50">
         <v>2.75E-2</v>
       </c>
-      <c r="Q18" s="114">
+      <c r="Q18" s="100">
         <f>P18*N18</f>
         <v>1.1000000000000001</v>
       </c>
@@ -2806,63 +2809,63 @@
     </row>
     <row r="19" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="94">
+      <c r="B19" s="84">
         <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="88" t="s">
+      <c r="C19" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="91" t="s">
+      <c r="E19" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="91" t="s">
+      <c r="F19" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="91" t="s">
+      <c r="G19" s="81" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="90" t="s">
+      <c r="H19" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="I19" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J19" s="91" t="s">
+      <c r="I19" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J19" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="K19" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L19" s="91">
+      <c r="K19" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L19" s="81">
         <v>1</v>
       </c>
-      <c r="M19" s="90">
+      <c r="M19" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N19" s="91">
+      <c r="N19" s="81">
         <v>15</v>
       </c>
-      <c r="O19" s="111" t="s">
+      <c r="O19" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P19" s="92">
+      <c r="P19" s="82">
         <v>6.54E-2</v>
       </c>
-      <c r="Q19" s="115">
+      <c r="Q19" s="101">
         <f t="shared" si="2"/>
         <v>0.98099999999999998</v>
       </c>
-      <c r="R19" s="91"/>
-      <c r="S19" s="92"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="82"/>
     </row>
     <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="94">
+      <c r="B20" s="84">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2903,13 +2906,13 @@
       <c r="N20" s="45">
         <v>15</v>
       </c>
-      <c r="O20" s="110" t="s">
+      <c r="O20" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P20" s="50">
         <v>7.1599999999999997E-2</v>
       </c>
-      <c r="Q20" s="114">
+      <c r="Q20" s="100">
         <f t="shared" si="2"/>
         <v>1.0739999999999998</v>
       </c>
@@ -2918,63 +2921,63 @@
     </row>
     <row r="21" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="94">
+      <c r="B21" s="84">
         <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="88" t="s">
+      <c r="C21" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="91" t="s">
+      <c r="E21" s="81" t="s">
         <v>208</v>
       </c>
-      <c r="F21" s="91" t="s">
+      <c r="F21" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="G21" s="91" t="s">
+      <c r="G21" s="81" t="s">
         <v>209</v>
       </c>
-      <c r="H21" s="90" t="s">
+      <c r="H21" s="80" t="s">
         <v>210</v>
       </c>
-      <c r="I21" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J21" s="91" t="s">
+      <c r="I21" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J21" s="81" t="s">
         <v>209</v>
       </c>
-      <c r="K21" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L21" s="91">
+      <c r="K21" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L21" s="81">
         <v>1</v>
       </c>
-      <c r="M21" s="90">
+      <c r="M21" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N21" s="91">
+      <c r="N21" s="81">
         <v>12</v>
       </c>
-      <c r="O21" s="111" t="s">
+      <c r="O21" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P21" s="92">
+      <c r="P21" s="82">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="Q21" s="115">
+      <c r="Q21" s="101">
         <f t="shared" si="2"/>
         <v>0.86399999999999988</v>
       </c>
-      <c r="R21" s="91"/>
-      <c r="S21" s="92"/>
+      <c r="R21" s="81"/>
+      <c r="S21" s="82"/>
     </row>
     <row r="22" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="94">
+      <c r="B22" s="84">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -3015,13 +3018,13 @@
       <c r="N22" s="45">
         <v>15</v>
       </c>
-      <c r="O22" s="110" t="s">
+      <c r="O22" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P22" s="50">
         <v>0.2276</v>
       </c>
-      <c r="Q22" s="114">
+      <c r="Q22" s="100">
         <f t="shared" si="2"/>
         <v>3.4140000000000001</v>
       </c>
@@ -3030,63 +3033,63 @@
     </row>
     <row r="23" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="94">
+      <c r="B23" s="84">
         <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="D23" s="89" t="s">
+      <c r="D23" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="91" t="s">
+      <c r="E23" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="F23" s="91" t="s">
+      <c r="F23" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="G23" s="91" t="s">
+      <c r="G23" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="H23" s="90" t="s">
+      <c r="H23" s="80" t="s">
         <v>213</v>
       </c>
-      <c r="I23" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J23" s="91" t="s">
+      <c r="I23" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J23" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="K23" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L23" s="91">
+      <c r="K23" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L23" s="81">
         <v>1</v>
       </c>
-      <c r="M23" s="90">
+      <c r="M23" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N23" s="91">
+      <c r="N23" s="81">
         <v>15</v>
       </c>
-      <c r="O23" s="111" t="s">
+      <c r="O23" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P23" s="92">
+      <c r="P23" s="82">
         <v>6.5600000000000006E-2</v>
       </c>
-      <c r="Q23" s="115">
+      <c r="Q23" s="101">
         <f t="shared" si="2"/>
         <v>0.9840000000000001</v>
       </c>
-      <c r="R23" s="91"/>
-      <c r="S23" s="92"/>
+      <c r="R23" s="81"/>
+      <c r="S23" s="82"/>
     </row>
     <row r="24" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="94">
+      <c r="B24" s="84">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
@@ -3127,13 +3130,13 @@
       <c r="N24" s="45">
         <v>120</v>
       </c>
-      <c r="O24" s="110" t="s">
+      <c r="O24" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P24" s="50">
         <v>4.6100000000000002E-2</v>
       </c>
-      <c r="Q24" s="114">
+      <c r="Q24" s="100">
         <f>P24*N24</f>
         <v>5.532</v>
       </c>
@@ -3142,63 +3145,63 @@
     </row>
     <row r="25" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="94">
+      <c r="B25" s="84">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="91" t="s">
+      <c r="E25" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="91" t="s">
+      <c r="F25" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="G25" s="91" t="s">
+      <c r="G25" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="H25" s="90" t="s">
+      <c r="H25" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J25" s="91" t="s">
+      <c r="I25" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="K25" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L25" s="91">
+      <c r="K25" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L25" s="81">
         <v>10</v>
       </c>
-      <c r="M25" s="90">
+      <c r="M25" s="80">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N25" s="91">
+      <c r="N25" s="81">
         <v>105</v>
       </c>
-      <c r="O25" s="111" t="s">
+      <c r="O25" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P25" s="92">
+      <c r="P25" s="82">
         <v>0.25779999999999997</v>
       </c>
-      <c r="Q25" s="115">
+      <c r="Q25" s="101">
         <f t="shared" si="2"/>
         <v>27.068999999999996</v>
       </c>
-      <c r="R25" s="91"/>
-      <c r="S25" s="92"/>
+      <c r="R25" s="81"/>
+      <c r="S25" s="82"/>
     </row>
     <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="94">
+      <c r="B26" s="84">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
@@ -3239,13 +3242,13 @@
       <c r="N26" s="45">
         <v>110</v>
       </c>
-      <c r="O26" s="110" t="s">
+      <c r="O26" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P26" s="50">
         <v>6.7900000000000002E-2</v>
       </c>
-      <c r="Q26" s="114">
+      <c r="Q26" s="100">
         <f t="shared" si="2"/>
         <v>7.4690000000000003</v>
       </c>
@@ -3254,62 +3257,62 @@
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="94">
+      <c r="B27" s="84">
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="78" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="89" t="s">
+      <c r="D27" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="91" t="s">
+      <c r="E27" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="91" t="s">
+      <c r="F27" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="91" t="s">
+      <c r="G27" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="I27" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J27" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="K27" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="91">
+      <c r="H27" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="I27" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J27" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="K27" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L27" s="81">
         <v>4</v>
       </c>
-      <c r="M27" s="90">
+      <c r="M27" s="80">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N27" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="O27" s="111" t="s">
-        <v>184</v>
-      </c>
-      <c r="P27" s="92" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q27" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="R27" s="91"/>
-      <c r="S27" s="92"/>
+      <c r="N27" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="O27" s="97" t="s">
+        <v>184</v>
+      </c>
+      <c r="P27" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q27" s="101" t="s">
+        <v>184</v>
+      </c>
+      <c r="R27" s="81"/>
+      <c r="S27" s="82"/>
     </row>
     <row r="28" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="94">
+      <c r="B28" s="84">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -3350,13 +3353,13 @@
       <c r="N28" s="45">
         <v>15</v>
       </c>
-      <c r="O28" s="110" t="s">
+      <c r="O28" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P28" s="50">
         <v>6.7400000000000002E-2</v>
       </c>
-      <c r="Q28" s="114">
+      <c r="Q28" s="100">
         <f t="shared" si="2"/>
         <v>1.0110000000000001</v>
       </c>
@@ -3365,63 +3368,63 @@
     </row>
     <row r="29" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="94">
+      <c r="B29" s="84">
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="88" t="s">
+      <c r="C29" s="78" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="89" t="s">
+      <c r="D29" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="91" t="s">
+      <c r="E29" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="91" t="s">
+      <c r="F29" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="G29" s="91" t="s">
+      <c r="G29" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="H29" s="90" t="s">
+      <c r="H29" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="I29" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J29" s="91" t="s">
+      <c r="I29" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="81" t="s">
         <v>153</v>
       </c>
-      <c r="K29" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L29" s="91">
+      <c r="K29" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" s="81">
         <v>1</v>
       </c>
-      <c r="M29" s="90">
+      <c r="M29" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N29" s="91">
+      <c r="N29" s="81">
         <v>50</v>
       </c>
-      <c r="O29" s="111" t="s">
+      <c r="O29" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P29" s="92">
+      <c r="P29" s="82">
         <v>1.47E-2</v>
       </c>
-      <c r="Q29" s="115">
+      <c r="Q29" s="101">
         <f t="shared" si="2"/>
         <v>0.73499999999999999</v>
       </c>
-      <c r="R29" s="91"/>
-      <c r="S29" s="92"/>
+      <c r="R29" s="81"/>
+      <c r="S29" s="82"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="105">
+      <c r="B30" s="91">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -3462,13 +3465,13 @@
       <c r="N30" s="71">
         <v>100</v>
       </c>
-      <c r="O30" s="112" t="s">
+      <c r="O30" s="98" t="s">
         <v>193</v>
       </c>
       <c r="P30" s="72">
         <v>1E-3</v>
       </c>
-      <c r="Q30" s="116">
+      <c r="Q30" s="102">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
@@ -3477,63 +3480,63 @@
     </row>
     <row r="31" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="94">
+      <c r="B31" s="84">
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="91" t="s">
+      <c r="D31" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="91" t="s">
+      <c r="E31" s="81" t="s">
         <v>232</v>
       </c>
-      <c r="F31" s="91" t="s">
+      <c r="F31" s="81" t="s">
         <v>233</v>
       </c>
-      <c r="G31" s="91" t="s">
+      <c r="G31" s="81" t="s">
         <v>234</v>
       </c>
-      <c r="H31" s="90" t="s">
+      <c r="H31" s="80" t="s">
         <v>235</v>
       </c>
-      <c r="I31" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J31" s="91" t="s">
+      <c r="I31" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J31" s="81" t="s">
         <v>236</v>
       </c>
-      <c r="K31" s="90" t="s">
+      <c r="K31" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="L31" s="91">
+      <c r="L31" s="81">
         <v>3</v>
       </c>
-      <c r="M31" s="90">
+      <c r="M31" s="80">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N31" s="91">
+      <c r="N31" s="81">
         <v>100</v>
       </c>
-      <c r="O31" s="111" t="s">
+      <c r="O31" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P31" s="92">
+      <c r="P31" s="82">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q31" s="115">
+      <c r="Q31" s="101">
         <f t="shared" si="2"/>
         <v>0.69</v>
       </c>
-      <c r="R31" s="91"/>
-      <c r="S31" s="92"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="82"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="94">
+      <c r="B32" s="84">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -3574,13 +3577,13 @@
       <c r="N32" s="45">
         <v>50</v>
       </c>
-      <c r="O32" s="110" t="s">
+      <c r="O32" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P32" s="50">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="Q32" s="114">
+      <c r="Q32" s="100">
         <f t="shared" si="2"/>
         <v>0.38999999999999996</v>
       </c>
@@ -3589,63 +3592,63 @@
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="94">
+      <c r="B33" s="84">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="89" t="s">
+      <c r="D33" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="91" t="s">
+      <c r="E33" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="91" t="s">
+      <c r="F33" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="109" t="s">
+      <c r="G33" s="95" t="s">
         <v>114</v>
       </c>
-      <c r="H33" s="90" t="s">
+      <c r="H33" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="I33" s="91" t="s">
+      <c r="I33" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="J33" s="91" t="s">
+      <c r="J33" s="81" t="s">
         <v>196</v>
       </c>
-      <c r="K33" s="90" t="s">
+      <c r="K33" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="L33" s="91">
+      <c r="L33" s="81">
         <v>2</v>
       </c>
-      <c r="M33" s="90">
+      <c r="M33" s="80">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N33" s="91">
+      <c r="N33" s="81">
         <v>100</v>
       </c>
-      <c r="O33" s="111" t="s">
+      <c r="O33" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P33" s="92">
+      <c r="P33" s="82">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q33" s="115">
+      <c r="Q33" s="101">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="R33" s="91"/>
-      <c r="S33" s="92"/>
+      <c r="R33" s="81"/>
+      <c r="S33" s="82"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="94">
+      <c r="B34" s="84">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -3686,13 +3689,13 @@
       <c r="N34" s="45">
         <v>100</v>
       </c>
-      <c r="O34" s="110" t="s">
+      <c r="O34" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P34" s="50">
         <v>1.4E-3</v>
       </c>
-      <c r="Q34" s="114">
+      <c r="Q34" s="100">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
@@ -3701,63 +3704,63 @@
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="94">
+      <c r="B35" s="84">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="88" t="s">
+      <c r="C35" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="89" t="s">
+      <c r="D35" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="91" t="s">
+      <c r="E35" s="81" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="91" t="s">
+      <c r="F35" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="G35" s="91" t="s">
+      <c r="G35" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="H35" s="90" t="s">
+      <c r="H35" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="I35" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J35" s="91" t="s">
+      <c r="I35" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="81" t="s">
         <v>198</v>
       </c>
-      <c r="K35" s="90" t="s">
+      <c r="K35" s="80" t="s">
         <v>172</v>
       </c>
-      <c r="L35" s="91">
+      <c r="L35" s="81">
         <v>1</v>
       </c>
-      <c r="M35" s="90">
+      <c r="M35" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N35" s="91">
+      <c r="N35" s="81">
         <v>100</v>
       </c>
-      <c r="O35" s="111" t="s">
+      <c r="O35" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P35" s="92">
+      <c r="P35" s="82">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="Q35" s="115">
+      <c r="Q35" s="101">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="R35" s="91"/>
-      <c r="S35" s="92"/>
+      <c r="R35" s="81"/>
+      <c r="S35" s="82"/>
     </row>
     <row r="36" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="94">
+      <c r="B36" s="84">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -3798,13 +3801,13 @@
       <c r="N36" s="45">
         <v>200</v>
       </c>
-      <c r="O36" s="110" t="s">
+      <c r="O36" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P36" s="50">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q36" s="114">
+      <c r="Q36" s="100">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
@@ -3813,63 +3816,63 @@
     </row>
     <row r="37" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="94">
+      <c r="B37" s="84">
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="88" t="s">
+      <c r="C37" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="89" t="s">
+      <c r="D37" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="91" t="s">
+      <c r="E37" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="91" t="s">
+      <c r="F37" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="G37" s="91" t="s">
+      <c r="G37" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="90" t="s">
+      <c r="H37" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="I37" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J37" s="91" t="s">
+      <c r="I37" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="81" t="s">
         <v>156</v>
       </c>
-      <c r="K37" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L37" s="91">
+      <c r="K37" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L37" s="81">
         <v>1</v>
       </c>
-      <c r="M37" s="90">
+      <c r="M37" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N37" s="91">
+      <c r="N37" s="81">
         <v>20</v>
       </c>
-      <c r="O37" s="111" t="s">
+      <c r="O37" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P37" s="92">
+      <c r="P37" s="82">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="Q37" s="115">
+      <c r="Q37" s="101">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
-      <c r="R37" s="91"/>
-      <c r="S37" s="92"/>
+      <c r="R37" s="81"/>
+      <c r="S37" s="82"/>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="94">
+      <c r="B38" s="84">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -3910,13 +3913,13 @@
       <c r="N38" s="45">
         <v>11</v>
       </c>
-      <c r="O38" s="110" t="s">
+      <c r="O38" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P38" s="50">
         <v>3.3553000000000002</v>
       </c>
-      <c r="Q38" s="114">
+      <c r="Q38" s="100">
         <f t="shared" si="2"/>
         <v>36.908300000000004</v>
       </c>
@@ -3925,63 +3928,63 @@
     </row>
     <row r="39" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="94">
+      <c r="B39" s="84">
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="88" t="s">
+      <c r="C39" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="89" t="s">
+      <c r="D39" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="91" t="s">
+      <c r="E39" s="81" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="91" t="s">
+      <c r="F39" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="G39" s="91" t="s">
+      <c r="G39" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="H39" s="90" t="s">
+      <c r="H39" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="I39" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J39" s="91" t="s">
+      <c r="I39" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J39" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="K39" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L39" s="91">
+      <c r="K39" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L39" s="81">
         <v>1</v>
       </c>
-      <c r="M39" s="90">
+      <c r="M39" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N39" s="91">
+      <c r="N39" s="81">
         <v>11</v>
       </c>
-      <c r="O39" s="111" t="s">
+      <c r="O39" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P39" s="92">
+      <c r="P39" s="82">
         <v>0.70960000000000001</v>
       </c>
-      <c r="Q39" s="115">
+      <c r="Q39" s="101">
         <f t="shared" si="2"/>
         <v>7.8056000000000001</v>
       </c>
-      <c r="R39" s="91"/>
-      <c r="S39" s="92"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="82"/>
     </row>
     <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="94">
+      <c r="B40" s="84">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -4022,13 +4025,13 @@
       <c r="N40" s="45">
         <v>105</v>
       </c>
-      <c r="O40" s="110" t="s">
+      <c r="O40" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P40" s="50">
         <v>0.11749999999999999</v>
       </c>
-      <c r="Q40" s="114">
+      <c r="Q40" s="100">
         <f t="shared" si="2"/>
         <v>12.337499999999999</v>
       </c>
@@ -4037,63 +4040,63 @@
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="94">
+      <c r="B41" s="84">
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="88" t="s">
+      <c r="C41" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="89" t="s">
+      <c r="D41" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="91" t="s">
+      <c r="E41" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="F41" s="91" t="s">
+      <c r="F41" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="G41" s="91" t="s">
+      <c r="G41" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="H41" s="90" t="s">
+      <c r="H41" s="80" t="s">
         <v>140</v>
       </c>
-      <c r="I41" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J41" s="91" t="s">
+      <c r="I41" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J41" s="81" t="s">
         <v>160</v>
       </c>
-      <c r="K41" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L41" s="91">
+      <c r="K41" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L41" s="81">
         <v>1</v>
       </c>
-      <c r="M41" s="90">
+      <c r="M41" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N41" s="91">
+      <c r="N41" s="81">
         <v>15</v>
       </c>
-      <c r="O41" s="111" t="s">
+      <c r="O41" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P41" s="92">
+      <c r="P41" s="82">
         <v>0.3513</v>
       </c>
-      <c r="Q41" s="115">
+      <c r="Q41" s="101">
         <f t="shared" si="2"/>
         <v>5.2694999999999999</v>
       </c>
-      <c r="R41" s="91"/>
-      <c r="S41" s="92"/>
+      <c r="R41" s="81"/>
+      <c r="S41" s="82"/>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="94">
+      <c r="B42" s="84">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -4134,13 +4137,13 @@
       <c r="N42" s="45">
         <v>25</v>
       </c>
-      <c r="O42" s="110" t="s">
+      <c r="O42" s="96" t="s">
         <v>193</v>
       </c>
       <c r="P42" s="50">
         <v>8.1199999999999994E-2</v>
       </c>
-      <c r="Q42" s="114">
+      <c r="Q42" s="100">
         <f t="shared" si="2"/>
         <v>2.0299999999999998</v>
       </c>
@@ -4149,255 +4152,255 @@
     </row>
     <row r="43" spans="1:19" s="75" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="73"/>
-      <c r="B43" s="94">
+      <c r="B43" s="84">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="88" t="s">
+      <c r="C43" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="79" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="81" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="G43" s="81" t="s">
         <v>237</v>
       </c>
-      <c r="D43" s="89" t="s">
-        <v>184</v>
-      </c>
-      <c r="E43" s="91" t="s">
-        <v>241</v>
-      </c>
-      <c r="F43" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="G43" s="91" t="s">
+      <c r="H43" s="80" t="s">
+        <v>130</v>
+      </c>
+      <c r="I43" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J43" s="81" t="s">
         <v>238</v>
       </c>
-      <c r="H43" s="90" t="s">
-        <v>130</v>
-      </c>
-      <c r="I43" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J43" s="91" t="s">
-        <v>239</v>
-      </c>
-      <c r="K43" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L43" s="91">
+      <c r="K43" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L43" s="81">
         <v>11</v>
       </c>
-      <c r="M43" s="90">
+      <c r="M43" s="80">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="N43" s="91">
+      <c r="N43" s="81">
         <v>115</v>
       </c>
-      <c r="O43" s="111" t="s">
+      <c r="O43" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P43" s="92">
+      <c r="P43" s="82">
         <v>0.1517</v>
       </c>
-      <c r="Q43" s="115">
+      <c r="Q43" s="101">
         <f t="shared" si="2"/>
         <v>17.445499999999999</v>
       </c>
-      <c r="R43" s="91"/>
-      <c r="S43" s="92"/>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
     </row>
     <row r="44" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="94">
+      <c r="B44" s="84">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="88" t="s">
-        <v>237</v>
-      </c>
-      <c r="D44" s="89" t="s">
-        <v>184</v>
-      </c>
-      <c r="E44" s="91" t="s">
+      <c r="C44" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="79" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="F44" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="G44" s="81" t="s">
+        <v>239</v>
+      </c>
+      <c r="H44" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="F44" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="G44" s="91" t="s">
-        <v>240</v>
-      </c>
-      <c r="H44" s="90" t="s">
+      <c r="I44" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J44" s="81" t="s">
         <v>243</v>
       </c>
-      <c r="I44" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J44" s="91" t="s">
-        <v>244</v>
-      </c>
-      <c r="K44" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L44" s="91">
+      <c r="K44" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L44" s="81">
         <v>1</v>
       </c>
-      <c r="M44" s="90">
+      <c r="M44" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N44" s="91">
+      <c r="N44" s="81">
         <v>15</v>
       </c>
-      <c r="O44" s="111" t="s">
+      <c r="O44" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P44" s="92">
+      <c r="P44" s="82">
         <v>0.34610000000000002</v>
       </c>
-      <c r="Q44" s="115">
+      <c r="Q44" s="101">
         <f t="shared" si="2"/>
         <v>5.1915000000000004</v>
       </c>
-      <c r="R44" s="91"/>
-      <c r="S44" s="92"/>
+      <c r="R44" s="81"/>
+      <c r="S44" s="82"/>
     </row>
     <row r="45" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="94">
+      <c r="B45" s="84">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="88" t="s">
-        <v>237</v>
-      </c>
-      <c r="D45" s="89" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" s="91" t="s">
+      <c r="C45" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="D45" s="79" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="81" t="s">
+        <v>247</v>
+      </c>
+      <c r="F45" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="G45" s="81" t="s">
+        <v>244</v>
+      </c>
+      <c r="H45" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="F45" s="91" t="s">
-        <v>185</v>
-      </c>
-      <c r="G45" s="91" t="s">
-        <v>245</v>
-      </c>
-      <c r="H45" s="90" t="s">
-        <v>249</v>
-      </c>
-      <c r="I45" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="J45" s="91" t="s">
-        <v>252</v>
-      </c>
-      <c r="K45" s="90" t="s">
-        <v>184</v>
-      </c>
-      <c r="L45" s="91">
+      <c r="I45" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J45" s="81" t="s">
+        <v>251</v>
+      </c>
+      <c r="K45" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="L45" s="81">
         <v>1</v>
       </c>
-      <c r="M45" s="90">
+      <c r="M45" s="80">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N45" s="91">
+      <c r="N45" s="81">
         <v>11</v>
       </c>
-      <c r="O45" s="111" t="s">
+      <c r="O45" s="97" t="s">
         <v>193</v>
       </c>
-      <c r="P45" s="92">
+      <c r="P45" s="82">
         <v>0.68320000000000003</v>
       </c>
-      <c r="Q45" s="115">
+      <c r="Q45" s="101">
         <f t="shared" si="2"/>
         <v>7.5152000000000001</v>
       </c>
-      <c r="R45" s="91"/>
-      <c r="S45" s="92"/>
+      <c r="R45" s="81"/>
+      <c r="S45" s="82"/>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B46" s="94">
+        <v>253</v>
+      </c>
+      <c r="B46" s="84">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="106" t="s">
-        <v>237</v>
-      </c>
-      <c r="D46" s="107" t="s">
-        <v>184</v>
-      </c>
-      <c r="E46" s="108" t="s">
-        <v>247</v>
-      </c>
-      <c r="F46" s="108" t="s">
+      <c r="C46" s="92" t="s">
+        <v>255</v>
+      </c>
+      <c r="D46" s="93" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="F46" s="94" t="s">
         <v>185</v>
       </c>
-      <c r="G46" s="108" t="s">
-        <v>246</v>
-      </c>
-      <c r="H46" s="118" t="s">
+      <c r="G46" s="94" t="s">
+        <v>245</v>
+      </c>
+      <c r="H46" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="I46" s="94" t="s">
+        <v>184</v>
+      </c>
+      <c r="J46" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="I46" s="108" t="s">
-        <v>184</v>
-      </c>
-      <c r="J46" s="108" t="s">
-        <v>251</v>
-      </c>
-      <c r="K46" s="118" t="s">
-        <v>184</v>
-      </c>
-      <c r="L46" s="108">
+      <c r="K46" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="L46" s="94">
         <v>1</v>
       </c>
-      <c r="M46" s="118">
+      <c r="M46" s="104">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N46" s="108">
+      <c r="N46" s="94">
         <v>11</v>
       </c>
-      <c r="O46" s="119" t="s">
+      <c r="O46" s="105" t="s">
         <v>193</v>
       </c>
-      <c r="P46" s="113">
+      <c r="P46" s="99">
         <v>0.96099999999999997</v>
       </c>
-      <c r="Q46" s="120">
+      <c r="Q46" s="106">
         <f t="shared" si="2"/>
         <v>10.571</v>
       </c>
-      <c r="R46" s="108"/>
-      <c r="S46" s="113"/>
+      <c r="R46" s="94"/>
+      <c r="S46" s="99"/>
     </row>
     <row r="47" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="B47" s="117"/>
-      <c r="C47" s="95"/>
-      <c r="D47" s="96"/>
-      <c r="E47" s="97"/>
-      <c r="F47" s="98"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="98"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="98"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="100" t="s">
+      <c r="B47" s="103"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="86"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="88"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="88"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="88"/>
+      <c r="K47" s="89"/>
+      <c r="L47" s="89"/>
+      <c r="M47" s="89"/>
+      <c r="N47" s="115" t="s">
         <v>220</v>
       </c>
-      <c r="O47" s="101"/>
-      <c r="P47" s="101"/>
-      <c r="Q47" s="102">
+      <c r="O47" s="116"/>
+      <c r="P47" s="116"/>
+      <c r="Q47" s="90">
         <f>SUM(Q10:Q46)</f>
         <v>161.08609999999999</v>
       </c>
-      <c r="R47" s="103"/>
-      <c r="S47" s="104"/>
+      <c r="R47" s="111"/>
+      <c r="S47" s="112"/>
     </row>
     <row r="48" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
@@ -4413,17 +4416,17 @@
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
       <c r="M48" s="10"/>
-      <c r="N48" s="85" t="s">
+      <c r="N48" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="O48" s="86"/>
-      <c r="P48" s="86"/>
+      <c r="O48" s="118"/>
+      <c r="P48" s="118"/>
       <c r="Q48" s="67">
         <f>Q47/10</f>
         <v>16.108609999999999</v>
       </c>
-      <c r="R48" s="83"/>
-      <c r="S48" s="84"/>
+      <c r="R48" s="113"/>
+      <c r="S48" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4511,15 +4514,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="78"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="108"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4569,7 +4572,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="79"/>
+      <c r="S3" s="109"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4594,7 +4597,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="110"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4619,7 +4622,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="80"/>
+      <c r="S5" s="110"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4640,7 +4643,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="80"/>
+      <c r="S6" s="110"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4661,7 +4664,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="80"/>
+      <c r="S7" s="110"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4682,7 +4685,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="80"/>
+      <c r="S8" s="110"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6605,17 +6608,17 @@
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="36"/>
-      <c r="N43" s="85" t="s">
+      <c r="N43" s="117" t="s">
         <v>220</v>
       </c>
-      <c r="O43" s="86"/>
-      <c r="P43" s="86"/>
+      <c r="O43" s="118"/>
+      <c r="P43" s="118"/>
       <c r="Q43" s="66">
         <f>SUM(Q10:Q42)</f>
         <v>9771.9939999999988</v>
       </c>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="R43" s="119"/>
+      <c r="S43" s="120"/>
     </row>
     <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -6631,17 +6634,17 @@
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
-      <c r="N44" s="85" t="s">
+      <c r="N44" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="O44" s="86"/>
-      <c r="P44" s="86"/>
+      <c r="O44" s="118"/>
+      <c r="P44" s="118"/>
       <c r="Q44" s="67">
         <f>Q43/1000</f>
         <v>9.7719939999999994</v>
       </c>
-      <c r="R44" s="83"/>
-      <c r="S44" s="84"/>
+      <c r="R44" s="113"/>
+      <c r="S44" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="5">
